--- a/reports/quote_request/report.xlsx
+++ b/reports/quote_request/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="157">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc5f-b3ae-7721-af82-09855e44935e</t>
+    <t>01a0cce1-6165-70b3-957d-80fbb84ddf37</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b5-7980-b56a-9b035d16741a</t>
+    <t>01a0cce1-616e-7210-909f-7e5d1c18b4f1</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -360,8 +360,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_097f8bf2fe8e699d006ab34bb4486087d2a06ce236430e6867", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0u0bS_InBim6hoX7C9Zptxg1LrYo5tGvjqUNuZyPOEUsnD9wz2LVvWn7EJZjuipnaV5lK4ORx4CtWQH1_nLJSY6gXMViBAF3J8ZhWeawimfArZ1y1wykpX3iHH2NT5A0WMkBqZ0jG7699SpgfToibu4jIQusdQ5KtAIgWMfq9V2MQaQTo4xlpfJC9PZCRtcXm-ZQMNHEOP6DpS95d2f29enm-PmpGNEQ9DcqZDnYKEP1eB9sNiYz8jeXROI1Yg4VC6FmjLIGVjj_DP9poKANhYXkrs0YgtpcUWs_0pbHY_cbk3fKK4BO3z7Lm-d-ROR739Ue8g8GmS0qWp6d-2P_aAVYkqtHUfMDptm_EYa2HeRSZzulos8IwZ0nGrXl-ndcIQieSuTE8PVcbzv2oBw5rRV8ObI5VxHJIZnpfMVwc8JQ_YtGdoFCu0HGSYGqqbOrskDQ5R3ndpf5RO5Ut443qDtchswh6NvOq8FHTIJrjAYpJ72E3I3BZdWDWMMcAS85DZ_jYNY8Rm4D_vGYTsPMKEmYN2c_8yrZM3IMw_5yG9ER5_-CQSEJ_C90la0KqoiVgd35Vy7Ct1fCU80EDihfQPLITkuu62-LvEKp01RxlThGtAt7P63UwSUwxSLOVSM7xjF1u1VWXPdFluTpX0PZo1PtMZQQvQHxmeUgydb4dKv-OcQRM-U22g_FRyCaNYbniYazO4W-cgMdKbHpdW4eo7kHLRCU0kWVo7sfKdeKkvgrBXrAoN8h6LB4P3L0eRJLroLZ0aZ6yb8vawtMYYHKXwS434mv7Othwnl4yE6JTtndMZTKzEuPlCn5c-woDCIuizb65abzvaqXwSVu52--mua_nVvbJWuTrkTNEi4gDd-wT9pkvg1HB-kzH69lKnOQiLMRpu6rITvZyI4Vm0NMBk-U-kMg3T5igEFZz_Qc4kVwopNNTQbQtsYn6yQhauM4tEHoZT81gdY_zo4rSBOjP-it6KtAhUBriknoEzcv0y6eLDEZYNFCYY-VeD8UW21T6P94pcJ10dkYWpcp3oO4mdiB1iBprXOUMIBnuxS20Nnj9xImhfriHNyfnAXXugsw7q5nG8bGn-RHll9CT94QL-xdrKqwGL2LIMaMBXZmAN2r7K4yt-f6UHLRTHZFZLyy2-WCyw-586jj9meXkAFXZoUi_DfMV9kZHzJM06rK4hT0ClpzO5aCTY14gJ2O6OgCOp-5ufFZqG5uRKNoWEzUgANqb-FPSGbOfeczJ-fyE0dqUCcqGMgPoC1hstNQWuOd03mfrEK4Wsv7Qiae4vX9j_8vKSPckw49opPNnBDMIO7cs5EEyJPLs9pCdHb-F38Vz6ypYZj6i-0slXOZ2vaYu-2SqIeD9HBfoWGIg3Q_n1HzJWmXDKmjkJAQNW9pUCI0dOoXZr7rgyDDciiF94wbniM7usmWe0nZ0dycV0hLxaUqck="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request contains two material conflicts: it asks for 500 invitations but says all 650 guests must receive one, and it asks for individually addressed invitations while also requiring identical text with no variable printing. The delivery instruction suggests you will mail them yourselves, but it is unclear whether the printer should print or apply recipient addresses.\",\"text\":\"Should the quote be for 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all copies be identical and you will handle all addressing and mailing after receiving one office batch?\"}", "call_id": "call_H7Gp596s6z8GDVdl2qVp9c2F", "id": "fc_097f8bf2fe8e699d006ab34bb4d14887d28fbc673fccfa9243", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request contains two material conflicts: it asks for 500 invitations but says all 650 guests must receive one, and it asks for individually addressed invitations while also requiring identical text with no variable printing. The delivery instruction suggests you will mail them yourselves, but it is unclear whether the printer should print or apply recipient addresses.", "text": "Should the quote be for 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all copies be identical and you will handle all addressing and mailing after receiving one office batch?"}, "id": "call_H7Gp596s6z8GDVdl2qVp9c2F", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0c1d5dd7d637d504006ab36ce68a3c87d2be22fc4920ffd396", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2znOmFUz75G8RO033GJWf6EZCl4UNa0xgCXsb422ShMxrR0h4QhWXwsltqh8SPAVt_BhXbm3Dxec7fw5m1gfJl972_FWek47J7mHq9LHmj2RaL6C65p5axWqLepbKxOxlNKpG19C-6javLcoKSxvwkHKDsYE8iFQhlHZjxNu1DXTyflmk5lpSP-2c_HQX95sA1eKXHji0oJTjNC8wy_CYsCfWEnwfNhiR0CawCZ85RvQ5y9xsjPuh84wL87_fwIZUbL8fNY9ajEU0vzcU9OZ13Tcey9NM6YENhpDjiEeBnLlfg8YlqpHtIndYXCZfjxOBAWL0PLHU_ksQ5AvWJTLVil8u7GMCq-OaxQLR8gaULleMvrYxw995hZmckjsF2ULYDhP0psIkk-6o1Klez4K3tTq7IPVzvjgNMKVth9K679sW-BdithDY2Yc8sNQWYjcMgRRO3xvu64zNhiznWUl_UmZSn1RW6QrLe3eycx08LCCmikGUlE7lrvEpocH3d7rU3S13ZanFab9oaZlP3ZAGmqAH1gJu86FyZTxgqnQfx7GVE9zX-beJZUeOW4YPTnH-zI1qRzZfMcdy0MXN0mnaPcFWU4t10ZhrxXQ8BJ41IxDxo1Z_KD2yF0B-qH1uRBgCWtLL64oTVFIHZBxbjgNt_5Gsa6chV9wTCrtYpImaXhSrW1r4rEP7bI9OtR7vK7OEj9JZGom43YqXvNad-ZoJarFMunI9o_WMMdc1uHf_4Q6d8Msm1NXYPWuDzfVEs_KOCqwedkzCu8hCDhPW0akfMP0schPRiEcQ3QH7BYIRMc48DEiYZxF2JZWFE2hU6NTZIkkG7NpDPyV6LlloxuN-U6YFmQDJo-3_LoNtfgOG-iRsl5TIHsa3sv5I0kNzrtFq-iQRdPB01r4xUwmsM-6ExgPW33TOeokIX6u7_uztvw1OEBtBfPSuMWdlxynduB-NyjE3SpbJ7FwE3PDvThhHMol8IldatOiaZH55nMXSs00gw9hXBjsUw_HXBsl6s204ZmXR5mwe3u3ySGqCq5Ye61t6fSksVkTw6qMHfL-Q-sy6ZHw9ctOraIGwOUigIBI7RQ3ixaEAWQQkGgChiGb5_ZIUINuH5GAVYr5n_5K7geAJd4quugfU8VybyFeAm8Qzh0temShCgYOnbfc8nGo9q_FD--vThON1JXlELnc-64TJCcoQZheX91lC-GFgtfpWwKTa3FMJ49AHjBWyg4adH9DCGlQvdtUqt4xCYdewdcALKTwsuo8-wn6fy3NwpfTqQiJLI-ncxecqBx4xxQojQXoxNBOcnBRmcB78JLDxIj7YvjVCe8APri8r118JULcXIFXlbvfNijCnk8YKGNqi7IX7X1Y5cVR-K4tQo-_vC3XegUa-egNOi36_Jo_5xCOsSgbWcUAvZkGJulijvQLmMSMxoxojh0cNFccRfSWwWkOwKv84tnTxYHiVJDsiwgcNGL-HnooUVtjLA9R5yhzhLKN5J5GfsqpiWQZAJg6L64I0GOQ9xC4A0WEbtoKMePCLGgheadUDf3h5iJgmXD_jbDnA=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request has two material conflicts: 500 invitations cannot cover 650 guests if each guest must receive one, and individually addressing them requires recipient-specific information or variable printing, which conflicts with using exactly the same text on every copy.\",\"text\":\"Should the order be for 650 invitations, and do you want each invitation individually addressed? If so, please confirm whether recipient names/addresses should be variable-printed or supplied separately; otherwise, clarify what you mean by \u201cindividually addressed\u201d while keeping identical text.\"}", "call_id": "call_eDH551q9MfMltpzk9bCVU808", "id": "fc_0c1d5dd7d637d504006ab36ce783ec87d2a9e4ceb1960dd50a", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request has two material conflicts: 500 invitations cannot cover 650 guests if each guest must receive one, and individually addressing them requires recipient-specific information or variable printing, which conflicts with using exactly the same text on every copy.", "text": "Should the order be for 650 invitations, and do you want each invitation individually addressed? If so, please confirm whether recipient names/addresses should be variable-printed or supplied separately; otherwise, clarify what you mean by \u201cindividually addressed\u201d while keeping identical text."}, "id": "call_eDH551q9MfMltpzk9bCVU808", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -373,24 +373,14 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc5f-e6bf-7681-8636-86cb3d48ea53</t>
+    <t>01a0cce1-b698-79e0-97be-7b21c9eb79a4</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>[{"id": "rs_08128df96d415dab006ab34bc1532c87d285906ca7501a2f36", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0vDa2zzUsL6_KfsId9poxlgrMRYemZD8s2-5Qiv8-GqezovFsIEWDu2ygqmitGs1l63atItgcfMG4gm6s06ImivX016jVhZNwGdNrgmA0rHDYsJdD8OHTHhl7KeZri1_dFBypzCUt273bcv4acchcbaxVa-CfrTkcBBujWP4aZJgmO2aDtOBZaO122D-F-BhhGw3--AU0y3wEXQ91tolnMIBcWsJZnOiNcY6RiPY3_Rw3ATkQA76YtXA2i5RI7jVPtsv8nAT4DnUSyp6wXTzj-B12Q9n36Hm0rZ3o7w7bumvCIl2Z36LNgI8OuEh7pkFZ8e_x_BDirMsiKZpZv0Nn4YFO2coFzWbCx3mJl0Dxx6DhjUBaYWr0gYv37Odb169O-O0fR5dT83j9IQRggGAFlms0biBUJUTWgU8UybRL7pIAarxtNwBa-zxOjHa0LXpeiLYCZ_c6sJ_N7Rk5oxHQag4UodznFXOGql5PPxsh-tHSzrtY0Ew_S_CWwI8lHeZ1JUyoWLNFDBzbT-LUbNYg-iOpyF8R7-28XnnUXpnU9XLvZqIf5nl07GUKbUn4agAbIxH8r2i9bOsUrLmhskRSlC2eWu8U3zhXTSS_OKssyH5UpDtOdQiz5ZK5QZQbW8Xt-Iq66abeIqUssP3KXKTcG61yHJZayn2thNPSlUjXSsY7aCDhFxrU4wVc5lugrPwGJMFw0wtUt0XG-kKcSi90eMXSfir8Veg3hMG9kXiV20LbOIeYyYvHO1H7EsHP4fSirD5Dkfy7gtUhRClm0TCA8reAMAQwy5I2aXorZ6wpnGKJiILn6gBnhM52Jta4ulKaIdHvBXBKDOEcCREHq6o08oMZPD3SkOyZq6i1wj4AcDP8XmuNkRCDSe1gF7bv8vbzO_nt7cEHtOg1VfiR0Fzhsj4oquJXp4P7vsrgFNMd4JxNeAkxMekx8ZAuZP7jmP2jUm5GunITSvo4qzC8O6FcQfh2nZCmOtqLmNaxwmGC3R71a45dyfnDH0TQI9DBKZT6I1DyhrWp43KezhOdSf0YHvJnrt8UH2Ma0otbgaKI8PRIVKYAoIK55VIolOHgVTgPNnL2USsbO-aBmbBMoXsHBRz4NEpAATIMIGpvPkdXIkp_HxUCD1jT-wObNjJgmrNzvCfpJOXIXwT5ejEV48F4gnZbS6Cn6NuO3ZDPnyTTEsM1UAH_pjjhqt9_eEZv92COG04GMDflZn3SShE0DCQ9lkIrChBAfaxeD14ewkIoKn4UCtuSEpudjSBoo_JUhwpZyGxDh-yTAXTmOZoG8LAz6Y7yfCuOzeUltsY6F4g9iYjQtrx9vyBCQccrqBWWvVjTmY3LbJnFkPFc9e-FqJUTRn5Lo4g2Y_Q2uSY6bLcabq-44-Mc3FbUDAbTBhvETeFytdim7NRaNtFzeohBdLjyzK6a1mv82Jyb5gObuPeH5yQz2U18y-f9K4CYZKYu5QkN3nJRP720eTULASFXTUaWrkm8Nzbi1zlpMmc8kWhV-H3Xtx_4vVCilmXeHneGT2OsTOZ1j1IB03Jap63VgBh8ED3cK3GF3pUXW__zFKJMbalgdtVRAVPxPi1zsasRiCnngov9NSJ6bH8Alnbw1g9aWvMy5N2EXDt1_0HJUsCLokoqI5xHH_bldC1UKfmrXM238TOE0Iu3ZA5fTNNpXQKIkkUC4HLpsf6zN0DKyc3q-wXl4SIHISKjmi9XGkCJp5iyFhW6X4F4SojKhyPyH1BbS4XA7YWLs91GHs3MhEQXsQ_GAGlDuTOqzTZWhcSSx-tTluSSEsZf1mNMq2mYYsD9Vl0gri9TjX3Ejjp1N46ch3-Vu2DoSUeAT5aMO2T8HU3uiljnZvCtMkaUyAJ0k1uiKBLXFgh6Y00_giCJx0UgQP572AowCeOmYP3GvHoqIYVX-WjoxJTbnIvHj7I0nXgOmoIptBN8QMtEA7npB93UvSZSBXCn0CdYs28gfeg0LMZr-h7uofoD2qUa0kGFQgvQDHKEO0MTWSfHTIsFgNU1k1W5uu0UnjD4SfPDZdBCMhB_SOkEsz0nQGXRhqioqGCQAhes8CEdjqhro3Slsq6gR8QVoZ3SI_6hc1pmURmfCIezOfUOo7mZcwnojgn94w8O8527M7XR-AXkmtazAY0mGeQoS5ADSGFxMljvFRG0qV3DDvD2Lsd_7KfcyGtzbicbpZ3l8hyYKkEd3s4eR22e0SbMZ-vfGoS06Yby6nrFjukjPEtEePoJk609tRIDjjKImSDQ=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The quantity and identical invitation text are now clear: 500 invitations, one per household, for 650 guests. However, \u201cput each guest\u2019s name and address on the envelopes\u201d conflicts slightly with one-envelope-per-household and does not specify how household names should appear. The production scope also needs confirmation because supplying a spreadsheet implies the printer will address the envelopes, despite the original request saying you would mail them yourselves.\",\"text\":\"Please confirm: should the printer print/address each of the 500 envelopes using the spreadsheet, with one envelope per household? If a household contains multiple guests, should the envelope list all guests\u2019 names or use one designated household/addressee name? The printer would deliver the 500 addressed envelopes and invitations in one batch to your office, and you would handle mailing\u2014correct?\"}", "call_id": "call_JjQIdcAcQcF8yDKcjkj1cj2v", "id": "fc_08128df96d415dab006ab34bc3143487d2aa77f38b5f9b490a", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The quantity and identical invitation text are now clear: 500 invitations, one per household, for 650 guests. However, \u201cput each guest\u2019s name and address on the envelopes\u201d conflicts slightly with one-envelope-per-household and does not specify how household names should appear. The production scope also needs confirmation because supplying a spreadsheet implies the printer will address the envelopes, despite the original request saying you would mail them yourselves.", "text": "Please confirm: should the printer print/address each of the 500 envelopes using the spreadsheet, with one envelope per household? If a household contains multiple guests, should the envelope list all guests\u2019 names or use one designated household/addressee name? The printer would deliver the 500 addressed envelopes and invitations in one batch to your office, and you would handle mailing\u2014correct?"}, "id": "call_JjQIdcAcQcF8yDKcjkj1cj2v", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0cc60-724b-79d0-9769-89c24988f6ba</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_05d14159d75f55a1006ab34be4e2e887d298fa12763cb8eb29", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0vmoFuPvQ6l_MYvCbSnG1SKw88uP0HyIgL1tCszlzDn37KFSiY7d1dIMqCwwz4WnQ9BkSThkrc9mZJcsKxOXb9Vx8hyppYKNKTidU35HSgYQxl2BhN9Laq8OBc7v6Lis0J3xjk8OTqSfgvjNy9b3pMDSH0epGwbSlN9pSsXQiLGw_9yBdbv4lLyepiR4URTUbIHkNkCdaed-RmY3Nb4wDus6Ow6GCZ_zET70FGyymgVIaCuAzZUAOUmijHla7y6woBEX2Pf2GtYm4t-WLbtZ1HqQo91ZPYli6XqTVnicVrl7NVKvmNm3kIDwMWtwHntOfAaQkDDQ_DUFY0NuzPt29LvoczrPQd7LBq2nTQL0Pg2FulyVs3Fcf_BSkAvTVQHwFzXORZOga411rf9yvZLmyZTtcny6xL1HUhJyPoPQd1u7vgNxlM0KeTWjCXVvUZejLVUB2pk5WUIJSGwrPGwCh9efUYXXl51ayBdBvHfliKarF8Y_vUbbxoh6R4X0UqheNewCjdxfRSBI7_nBpkslPBIek_byHQ4RwdCb99SM7dHeserjPcTgSnpbazAIlEBXyAi9SQFOQWU6vAD1GKojQSUbjaSRky4ae5WVdhR3od9SqpFcXx_45KlUCtAksqZDsg2_bKP46zVg_HmbTpq5fvAZNPolmZffk7WQH803ST8lMtGkKE7CECE2t1y-GBpza90mYVT7aAX2QfK1Nj_hLGVmsZw4j1Aih-_i7HxW-iQB8JWCW8j1JGvzO8UFljKN2l-c2P--XR5EmAEQk6oCFU89fkjJZF7s9BkYbO7OIJVYIPBWXcNV61J3xlTDQTwRS3WGOgmGCOLf5s74gEzjGDsV15pOFGdbvJOUt8HfvWVLigfD5djar7HrIw9hJKdUeooSkYAwzpGfxo3YbAvR0LF5GzRi3nGJN2bCzRcvaUroZ2dI9m3AHDUlFRRhI0T9caZupt4acEw5o93VfSUJ0cS3qrLK_Sz6irHF7uqRRD2I0Q4qEVKCYRnKR_elGA7KxtA4XvGJL6Tx4tp7mS6No1QiIR9V-w1beA5sSp4fJ5VVpNp8bmpNG3AmgXOQAZsVC6QK67AqCXZKtbvZd26DN9D6UEBPHAhOlqLTSe1DIWEgkdXkll99p8ndEJmvaefBPA_u0cpJuKwh7bWxgF2zsr5L8z2HfhJl9W8uiPnfwP_-9vGIAcJmOrVg3PkInw5bMHQaszeMkewG7wItbbMgmOH2CrO8hTQGvMbMKgozEo9SnSmcPm_GyBPRfWuwkL1jklqMQLoe8huomgRcIdZfIw8zK-cfbnVL3leycvFhLzimQd9eqN1QTCF9HOCOEoT_Ua1MC5fPgKp3UDR4jECpgNTI-xVasSaBn_4dOcnkkSHUkX1jtbeJkfXBNEhRIUywV2poyiW8vJiuaSfFrpFTrBwarIXxg9BMQvLqsmP4ybI4WH_0XQZJnl65Kkfn9RV6mOGGf24UC1FuaGuWdU_I08yYGXsT3OF7nPO_OJBS7Yzdk9_6FExqbd6XZEeQIGSsxlLqJoSCLCsNETYJx84i0MHDQ68fdtdzT-mG21zzcDqZcJEbrdkhEFwYU4bRAVpoVMpOymlfkes8L7Lh_ZDqXwWgBYhoNcVf53FTmSFP5yVFFYz31oeLGSCTAETNgfLY8LvDQlPhzc-ZnC39MAA0VGMF7eAOwO_-HQbn0a-DH17B5ccrJYY69oKhfQ2LXTiU8w1nwSLCGpW1Z1SBlooT7TkI8ninTFvkRg1LEGBwBXO5E1oz4UF_AyiGU0OyzBTHj2BrP-Tt6omJFK5j3eZME2PlT3tBvzJWWmOB3ONnzr3CzaKAO-QOf0gdABGN06elyyaPeQGxsg7EFg8_ngoDagADi1ERLvDKEQJnQcVpysHzKHrWIEtKftqXxtPWsec5BXQ_fA_fRibKDBJdh1_E2kYzPpHLiVJJZzD6u0FJSTzmLs="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"complete\",\"reason\":\"The clarification resolves the material quantity and addressing conflicts: 500 households means 500 identical invitations and 500 envelopes, with one spreadsheet row per household. The envelopes\u2014not the invitations\u2014will be individually addressed using the supplied names and addresses, and both items will be delivered together in one batch for the customer to mail.\",\"text\":\"Prepare a quote for Alex (alex@example.com) for 500 identical printed invitations with no variable text, plus 500 printed envelopes individually addressed from the customer\u2019s spreadsheet, one envelope per household/row. Deliver the invitations and addressed envelopes together in one batch to the customer\u2019s office; the customer will handle mailing. Envelope addressee names and addresses must be reproduced exactly as supplied.\"}", "call_id": "call_WKOY63dAwDwMh5DNDHoddbtM", "id": "fc_05d14159d75f55a1006ab34be63cec87d2b8bdf9f456b64c71", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "complete", "reason": "The clarification resolves the material quantity and addressing conflicts: 500 households means 500 identical invitations and 500 envelopes, with one spreadsheet row per household. The envelopes\u2014not the invitations\u2014will be individually addressed using the supplied names and addresses, and both items will be delivered together in one batch for the customer to mail.", "text": "Prepare a quote for Alex (alex@example.com) for 500 identical printed invitations with no variable text, plus 500 printed envelopes individually addressed from the customer\u2019s spreadsheet, one envelope per household/row. Deliver the invitations and addressed envelopes together in one batch to the customer\u2019s office; the customer will handle mailing. Envelope addressee names and addresses must be reproduced exactly as supplied."}, "id": "call_WKOY63dAwDwMh5DNDHoddbtM", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0d864b2ca1e38a23006ab36cfca06487d2ab204b69bb29728c", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2z9j4W3kooN1KD0xKDm5DxsTMZjxAMRaBh5f6FalAwtJltIO2yqm0jz8SmQgXdda88jZvVm9eUETmzx1piCS_yZ_v646N7RwciPiD5Q1dB-dZxrOEqTcZia9-_weSDsVgc5Fs6xWuyIYxIzXIGTsyYaBeUhwJvXJv6XelcW4eLgm_OQq5OjEt4-d5pY5iSdX1CpWXb9302YMa0PLHNiyXiqbSpY6u6wBjhVgMj9eTYlcDVAIdY9juHuTsCy0hiqEGqyU-49dijf6OIbslmGus2VUFEdVKSlLlgkxd2ZsNLBwgPMebZ75Wv2YFpF35vrtFh14XEa0wG_kpBjwmMHbq7Q-KTNThrPtO0zASTCNfKb4UEm0nhFBKlcEHd4CHJ_jQ1j1cJU82bLHUEjYKTVWRrNJjyxkrUDdkRnFn6r-srUxKHiSl3zuo0ni34T2ZP_bVxTR3DIrXAfq1_Uu67hZ9VeC0YLlZj4yMkyD8Mawab2gE0RroBBiqHKMrjWLAxMjP2uNH7XTZJSqJDhhql0XlO_B3l_ShyPW2CxPO1CmnO2i5Dgifc1ahi9soBra5_ZKEKobBnYsLsODMATF4hzUg5DG_dLBhCSo3wevSBXexcrCzDpU6nGHGXX_x8MtfsVUZRrOufKFi2vR65QbnLzxv3jrfZkOMNUQ6j8sGQVz3y_ZgvoPTtE0Awsxqw75DTrhV6PTFSCHJKbXG5mlphX4hpQi3T5i-h37t00hvq9fKE65radOk5dfQXdWDytWiapH0S5tjSKURXI6wTODnoLn5r0B1_2F7Mj3Hw09rYa5gzTJ6f8ZWZpjMwmTdO2xrDJj1eNsLAKVPbJdvMFtjBRrZjvCWh9dxMYpnajCg6Eew2bWQ0GoDU2nOewj8rcLtQkNKY11nwk6JcduAgyWA-YJ_xX7uhZ0cXvLutoErj7SHI8C1Zcbjo5kyN5MpER-JudM1Wv1hkxzmxF697nSU-oc8IuZoc9zOVtIJT1hQgfnKObOw3AMLMjBZOLTUS2S6-ZHoFIiD6qLoMKf-3WFt8dAWptunH8f1upSICzTGBECPFd0seqXsVuafCIL7CGWhlk7PJyBKT9dXoBT4T3TP1i_SE-6MXyq6Qt4NvFW-saMMbEuXZsDu9o2BXSFdqlOGIDcBnqksxwk6c7ZJSS0M1f2MENW_qOiCoDCV7zzsvO6kPG3yu1c6cYhCupaEes9mmtF5_fCoW36bLiz0w2GULrTksilBU8_23zjLC8k6nEJfA0Bx3YV11PSWGcjnq4DLpgYatFZCCemupzReNmFizOR1TaGpBF4SuOxgW3wz1IdFAzPClVDTgtNE9aH7w75YqeurSAZ1QKb3cYdfTPgt1-12xnjQ47pYo1p4XPClrQv1dOyR_mVHoGsTd0yBvgwf4Xb5GjaFgaVIKovQdGnA8YucbFe2ZEfWgVJQsLyiMbCuf6AEoZw8aIa-B5R6KwBSpWDzaVMcF7CYiQ31j-NImgNuKISdweTLmKjMcUsjipIniTOYNJ9ISZ3CtRe970zhE-HxwqPQ1PMx0VrK-tp6d59VMQUE91hy7DrxqrjcZo0jy98CKEjFa715WijapnbyCMxiev"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"complete\",\"reason\":\"The quantity and recipient scope are reconciled: 500 households among 650 guests, with one invitation per household. The invitation text is identical, and the household names and addresses will be printed on 500 envelopes using the customer's spreadsheet. Delivery and mailing responsibility are also clear.\",\"text\":\"Prepare a quote for 500 identical-text invitations and 500 envelopes, with each household's supplied name and address printed on its envelope. The customer will provide the spreadsheet, receive the complete order in one batch at their office, and handle mailing themselves.\"}", "call_id": "call_iV4eY6YTKofFQcS5UldKUg6W", "id": "fc_0d864b2ca1e38a23006ab36cfdfebc87d292aaf5c2ec7395e3", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "complete", "reason": "The quantity and recipient scope are reconciled: 500 households among 650 guests, with one invitation per household. The invitation text is identical, and the household names and addresses will be printed on 500 envelopes using the customer's spreadsheet. Delivery and mailing responsibility are also clear.", "text": "Prepare a quote for 500 identical-text invitations and 500 envelopes, with each household's supplied name and address printed on its envelope. The customer will provide the spreadsheet, receive the complete order in one batch at their office, and handle mailing themselves."}, "id": "call_iV4eY6YTKofFQcS5UldKUg6W", "type": "tool_call"}</t>
   </si>
   <si>
     <t>LangGraph</t>
@@ -411,7 +401,7 @@
     <t>Execute the begin workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b1-77a3-893b-6c5fd33b188d</t>
+    <t>01a0cce1-6169-71e2-8aab-9e6bd4736ee5</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -423,7 +413,7 @@
     <t>Execute the assess workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b2-72e3-804d-01eb34c489f5</t>
+    <t>01a0cce1-616b-7b12-a39a-e8bc1e07d74f</t>
   </si>
   <si>
     <t xml:space="preserve">        quote_interpreter</t>
@@ -432,19 +422,19 @@
     <t>Interpret quote scope and request human clarification when needed.</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b3-7490-bf29-d827c55ca539</t>
+    <t>01a0cce1-616b-7b12-a39a-e8cddd06482a</t>
   </si>
   <si>
     <t xml:space="preserve">            quote_interpreter</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b3-7490-bf29-d83d801bd75e</t>
+    <t>01a0cce1-616c-7af0-85c8-5eb3499a67ef</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cc5f-b3b4-7cb0-ba8b-ddf151a7053c</t>
+    <t>01a0cce1-616d-7960-bb2d-64b1a1fe878a</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -462,7 +452,7 @@
     <t>Execute the route_after_assessment workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc5f-c090-7422-9174-a0c38817c268</t>
+    <t>01a0cce1-6ff6-7e42-a8f5-334ac65d2743</t>
   </si>
   <si>
     <t xml:space="preserve">    ask</t>
@@ -474,13 +464,13 @@
     <t>Execute the ask workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc5f-c091-7fb3-83f4-2f65c3a245b0</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6b2-7970-9769-cb49463ab471</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6b5-77e2-bcc9-7ae32b342cf5</t>
+    <t>01a0cce1-6ff8-75b3-9b6b-131ec955b34f</t>
+  </si>
+  <si>
+    <t>01a0cce1-b68f-7c51-8560-adf8e99061cd</t>
+  </si>
+  <si>
+    <t>01a0cce1-b691-72a2-802b-a4c8eaf554cd</t>
   </si>
   <si>
     <t xml:space="preserve">        route_after_answer</t>
@@ -489,49 +479,22 @@
     <t>Execute the route_after_answer workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc5f-e6b6-76f2-ade6-39cf56a4bd80</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6b9-71d1-822a-561d6282d019</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6b9-71d1-822a-562a6847ca18</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6bb-7ac3-b3af-0be7c4e70de5</t>
-  </si>
-  <si>
-    <t>01a0cc5f-e6bd-74a0-a182-da8ffba208ed</t>
-  </si>
-  <si>
-    <t>01a0cc5f-fa01-7020-9aa5-103efa52c67d</t>
-  </si>
-  <si>
-    <t>01a0cc5f-fa03-7be2-8677-c2bfd1bc2379</t>
-  </si>
-  <si>
-    <t>01a0cc60-7240-7191-b09b-df3f860d74e5</t>
-  </si>
-  <si>
-    <t>01a0cc60-7244-71f2-a540-b114ee39df2d</t>
-  </si>
-  <si>
-    <t>01a0cc60-7245-7000-91ed-1e9f3b6f5a00</t>
-  </si>
-  <si>
-    <t>01a0cc60-7247-7861-8eaf-7abadc01c826</t>
-  </si>
-  <si>
-    <t>01a0cc60-7247-7861-8eaf-7ac54a7af9b4</t>
-  </si>
-  <si>
-    <t>01a0cc60-7249-7263-92aa-b8a04d16be3a</t>
-  </si>
-  <si>
-    <t>01a0cc60-724a-7961-b538-69992e8a0783</t>
-  </si>
-  <si>
-    <t>01a0cc60-80a1-7891-942a-30232802268f</t>
+    <t>01a0cce1-b691-72a2-802b-a4d1becd1d43</t>
+  </si>
+  <si>
+    <t>01a0cce1-b693-70e1-a394-b812adf39488</t>
+  </si>
+  <si>
+    <t>01a0cce1-b693-70e1-a394-b822b4212b7f</t>
+  </si>
+  <si>
+    <t>01a0cce1-b694-7e60-9fb8-2b73f2f4ff4b</t>
+  </si>
+  <si>
+    <t>01a0cce1-b695-74d2-8a78-82541c7a0a82</t>
+  </si>
+  <si>
+    <t>01a0cce1-c7a5-71c3-b636-cc0023379662</t>
   </si>
   <si>
     <t xml:space="preserve">    complete</t>
@@ -540,7 +503,7 @@
     <t>Execute the complete workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc60-80a2-77a2-a0d2-ca7d6497d269</t>
+    <t>01a0cce1-c7a6-7622-8620-9e4966d5a5ff</t>
   </si>
 </sst>
 </file>
@@ -947,7 +910,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1007,20 +970,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
-        <v>0.001149958134</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
+        <v>0.000589373172</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
-        <v>0.0013182</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
+        <v>0.0006756</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>115.0</v>
+        <v>59.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>132.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1031,20 +994,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
-        <v>0.001149958134</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
+        <v>0.000589373172</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
-        <v>0.0013182</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
+        <v>0.0006756</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>115.0</v>
+        <v>59.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>132.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1169,7 +1132,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1183,23 +1146,23 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1213,23 +1176,23 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409" customHeight="1">
@@ -1280,11 +1243,11 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1309,7 +1272,7 @@
         <v>94</v>
       </c>
       <c r="D18" s="4">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>95</v>
@@ -1359,15 +1322,15 @@
         <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="F20" s="2">
         <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B17),D20*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1411,7 +1374,7 @@
         <v>105</v>
       </c>
       <c r="D23" s="4">
-        <v>335</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
@@ -1425,23 +1388,23 @@
         <v>106</v>
       </c>
       <c r="D24" s="5">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="F24" s="2">
         <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!F17),D24*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="G24" s="5">
         <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="H24" s="5">
         <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
@@ -1455,23 +1418,23 @@
         <v>107</v>
       </c>
       <c r="D25" s="5">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="E25" s="2">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="F25" s="2">
         <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E17),D25*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="G25" s="5">
         <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="H25" s="5">
         <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409" customHeight="1">
@@ -1522,268 +1485,26 @@
       </c>
       <c r="E29" s="2">
         <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25)=4,SUM('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="F29" s="2">
         <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25)=4,SUM('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="4">
-        <v>751</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F31" s="2">
-        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!C17),D31*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="5">
-        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="5">
-        <v>751</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!B17),D32*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="24" customHeight="1">
-      <c r="A33" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="24" customHeight="1">
-      <c r="A34" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="4">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="24" customHeight="1">
-      <c r="A36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" s="5">
-        <v>104</v>
-      </c>
-      <c r="E36" s="2">
-        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="F36" s="2">
-        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!F17),D36*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="G36" s="5">
-        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H36" s="5">
-        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="24" customHeight="1">
-      <c r="A37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="5">
-        <v>166</v>
-      </c>
-      <c r="E37" s="2">
-        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="F37" s="2">
-        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!E17),D37*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="G37" s="5">
-        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-      <c r="H37" s="5">
-        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="409" customHeight="1">
-      <c r="A38" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="24" customHeight="1">
-      <c r="A39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="24" customHeight="1">
-      <c r="A40" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="2">
-        <f>IF(COUNT('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37)=4,SUM('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="F41" s="2">
-        <f>IF(COUNT('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37)=4,SUM('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="H41" s="5">
-        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE41">
+  <conditionalFormatting sqref="A2:AE29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1797,7 +1518,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE30"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1904,13 +1625,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -1919,7 +1640,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -1956,35 +1677,35 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1995,21 +1716,21 @@
         <v>32.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>3299.193</v>
+        <v>3729.158</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -2018,30 +1739,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.443</v>
+        <v>0.519</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -2050,10 +1771,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -2090,35 +1811,35 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2129,21 +1850,21 @@
         <v>32.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>3294.254</v>
+        <v>3724.375</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>47</v>
@@ -2152,13 +1873,13 @@
         <v>111</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2192,35 +1913,35 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2231,21 +1952,21 @@
         <v>32.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>3292.558</v>
+        <v>3721.981</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -2254,13 +1975,13 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" t="s">
         <v>131</v>
       </c>
-      <c r="H6" t="s">
-        <v>134</v>
-      </c>
       <c r="I6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J6" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2294,35 +2015,35 @@
       </c>
       <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V6" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W6" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X6" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2333,21 +2054,21 @@
         <v>32.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3291.458</v>
+        <v>3720.672</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -2356,13 +2077,13 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" t="s">
         <v>131</v>
-      </c>
-      <c r="H7" t="s">
-        <v>136</v>
-      </c>
-      <c r="I7" t="s">
-        <v>134</v>
       </c>
       <c r="J7" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2396,35 +2117,35 @@
       </c>
       <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2435,21 +2156,21 @@
         <v>32.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3289.153</v>
+        <v>3718.433</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>95</v>
@@ -2461,13 +2182,13 @@
         <v>493</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
         <v>96</v>
       </c>
       <c r="I8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2501,35 +2222,35 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>142.0</v>
+        <v>127.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000148651848</v>
+        <v>0.000132949188</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001704</v>
+        <v>0.0001524</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>5.8623264e-05</v>
       </c>
       <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.16e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000279681822</v>
+        <v>0.000277588134</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003206</v>
+        <v>0.0003182</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2543,21 +2264,21 @@
         <v>93</v>
       </c>
       <c r="AD8" s="1">
-        <v>3284.91</v>
+        <v>3716.362</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -2566,62 +2287,62 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.323</v>
+        <v>0.337</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -2630,22 +2351,22 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J11" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M11" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2670,60 +2391,60 @@
       </c>
       <c r="S11" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T11" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U11" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V11" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W11" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X11" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y11" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z11" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>4944.435</v>
+        <v>4376.078</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -2732,30 +2453,30 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" t="s">
         <v>145</v>
       </c>
-      <c r="H12" t="s">
-        <v>148</v>
-      </c>
       <c r="I12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AD12" s="1">
-        <v>2.065</v>
+        <v>1.455</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>47</v>
@@ -2764,30 +2485,30 @@
         <v>111</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AD13" s="1">
-        <v>0.467</v>
+        <v>0.299</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -2796,25 +2517,25 @@
         <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J14" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2839,60 +2560,60 @@
       </c>
       <c r="S14" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T14" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U14" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V14" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W14" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X14" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>4937.977</v>
+        <v>4370.533</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -2901,25 +2622,25 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2944,60 +2665,60 @@
       </c>
       <c r="S15" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T15" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U15" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V15" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W15" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X15" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>4935.422</v>
+        <v>4369.011</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -3006,25 +2727,25 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J16" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K16" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L16" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3049,60 +2770,60 @@
       </c>
       <c r="S16" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T16" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U16" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V16" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W16" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X16" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y16" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z16" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>4933.177</v>
+        <v>4367.631</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B17" s="1">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -3111,25 +2832,25 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I17" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J17" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K17" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L17" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M17" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3154,60 +2875,60 @@
       </c>
       <c r="S17" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T17" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U17" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V17" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W17" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X17" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y17" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z17" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>4929.877</v>
+        <v>4365.756</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>95</v>
@@ -3216,28 +2937,28 @@
         <v>111</v>
       </c>
       <c r="F18" s="1">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H18" t="s">
         <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J18" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>607.0</v>
+        <v>623.0</v>
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000105905718</v>
+        <v>0.000108697302</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001214</v>
+        <v>0.0001246</v>
       </c>
       <c r="M18" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3262,63 +2983,63 @@
       </c>
       <c r="S18" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>185.0</v>
+        <v>131.0</v>
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00019366614</v>
+        <v>0.000137136564</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000222</v>
+        <v>0.0001572</v>
       </c>
       <c r="V18" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>150.0</v>
+        <v>63.0</v>
       </c>
       <c r="W18" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.0001570266</v>
+        <v>6.5951172e-05</v>
       </c>
       <c r="X18" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.00018</v>
+        <v>7.56e-05</v>
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000456598458</v>
+        <v>0.000311785038</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0005234</v>
+        <v>0.0003574</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>36.0</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>112</v>
       </c>
       <c r="AD18" s="1">
-        <v>4926.947</v>
+        <v>4362.213</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -3327,816 +3048,55 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.914</v>
+        <v>0.348</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H20" t="s">
-        <v>157</v>
-      </c>
-      <c r="I20" t="s">
-        <v>147</v>
-      </c>
       <c r="AD20" s="1">
-        <v>0.387</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" ht="54" customHeight="1">
-      <c r="A21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K21" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L21" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>0</v>
-      </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T21" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U21" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V21" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W21" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X21" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB21" s="5">
-        <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>3683.237</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" ht="54" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H22" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>1.988</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" ht="54" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I23" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>0.379</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="54" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K24" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L24" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M24" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P24" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T24" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U24" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V24" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W24" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X24" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y24" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z24" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA24" s="5">
-        <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB24" s="5">
-        <f>IF(ISNUMBER(Z24),ROUND(Z24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>3674.826</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" ht="54" customHeight="1">
-      <c r="A25" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K25" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L25" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M25" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T25" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U25" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V25" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W25" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X25" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y25" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z25" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA25" s="5">
-        <f>IF(ISNUMBER(Y25),ROUND(Y25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB25" s="5">
-        <f>IF(ISNUMBER(Z25),ROUND(Z25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AD25" s="1">
-        <v>3673.373</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" ht="54" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K26" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L26" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M26" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T26" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U26" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V26" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W26" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X26" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y26" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z26" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA26" s="5">
-        <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB26" s="5">
-        <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>3671.9</v>
-      </c>
-      <c r="AE26" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" ht="54" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="1">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H27" t="s">
-        <v>164</v>
-      </c>
-      <c r="I27" t="s">
-        <v>163</v>
-      </c>
-      <c r="J27" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K27" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L27" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M27" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T27" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U27" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V27" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W27" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X27" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y27" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z27" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA27" s="5">
-        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB27" s="5">
-        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>3669.979</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="54" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="1">
-        <v>751</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H28" t="s">
-        <v>117</v>
-      </c>
-      <c r="I28" t="s">
-        <v>164</v>
-      </c>
-      <c r="J28" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>751.0</v>
-      </c>
-      <c r="K28" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.000131029974</v>
-      </c>
-      <c r="L28" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001502</v>
-      </c>
-      <c r="M28" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>166.0</v>
-      </c>
-      <c r="T28" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.000173776104</v>
-      </c>
-      <c r="U28" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001992</v>
-      </c>
-      <c r="V28" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="W28" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000108871776</v>
-      </c>
-      <c r="X28" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0001248</v>
-      </c>
-      <c r="Y28" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.000413677854</v>
-      </c>
-      <c r="Z28" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004742</v>
-      </c>
-      <c r="AA28" s="5">
-        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
-      </c>
-      <c r="AB28" s="5">
-        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>3667.604</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" ht="54" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>0.234</v>
-      </c>
-      <c r="AE29" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" ht="54" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H30" t="s">
-        <v>168</v>
-      </c>
-      <c r="I30" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>0.439</v>
-      </c>
-      <c r="AE30" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE30">
+  <conditionalFormatting sqref="A2:AE20">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>

--- a/reports/quote_request/report.xlsx
+++ b/reports/quote_request/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="170">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce1-6165-70b3-957d-80fbb84ddf37</t>
+    <t>01a0d132-b474-79e2-bebb-1d3cde2984ea</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce1-616e-7210-909f-7e5d1c18b4f1</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d132-b47a-7da0-b744-558a9097def7</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -360,8 +360,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0c1d5dd7d637d504006ab36ce68a3c87d2be22fc4920ffd396", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2znOmFUz75G8RO033GJWf6EZCl4UNa0xgCXsb422ShMxrR0h4QhWXwsltqh8SPAVt_BhXbm3Dxec7fw5m1gfJl972_FWek47J7mHq9LHmj2RaL6C65p5axWqLepbKxOxlNKpG19C-6javLcoKSxvwkHKDsYE8iFQhlHZjxNu1DXTyflmk5lpSP-2c_HQX95sA1eKXHji0oJTjNC8wy_CYsCfWEnwfNhiR0CawCZ85RvQ5y9xsjPuh84wL87_fwIZUbL8fNY9ajEU0vzcU9OZ13Tcey9NM6YENhpDjiEeBnLlfg8YlqpHtIndYXCZfjxOBAWL0PLHU_ksQ5AvWJTLVil8u7GMCq-OaxQLR8gaULleMvrYxw995hZmckjsF2ULYDhP0psIkk-6o1Klez4K3tTq7IPVzvjgNMKVth9K679sW-BdithDY2Yc8sNQWYjcMgRRO3xvu64zNhiznWUl_UmZSn1RW6QrLe3eycx08LCCmikGUlE7lrvEpocH3d7rU3S13ZanFab9oaZlP3ZAGmqAH1gJu86FyZTxgqnQfx7GVE9zX-beJZUeOW4YPTnH-zI1qRzZfMcdy0MXN0mnaPcFWU4t10ZhrxXQ8BJ41IxDxo1Z_KD2yF0B-qH1uRBgCWtLL64oTVFIHZBxbjgNt_5Gsa6chV9wTCrtYpImaXhSrW1r4rEP7bI9OtR7vK7OEj9JZGom43YqXvNad-ZoJarFMunI9o_WMMdc1uHf_4Q6d8Msm1NXYPWuDzfVEs_KOCqwedkzCu8hCDhPW0akfMP0schPRiEcQ3QH7BYIRMc48DEiYZxF2JZWFE2hU6NTZIkkG7NpDPyV6LlloxuN-U6YFmQDJo-3_LoNtfgOG-iRsl5TIHsa3sv5I0kNzrtFq-iQRdPB01r4xUwmsM-6ExgPW33TOeokIX6u7_uztvw1OEBtBfPSuMWdlxynduB-NyjE3SpbJ7FwE3PDvThhHMol8IldatOiaZH55nMXSs00gw9hXBjsUw_HXBsl6s204ZmXR5mwe3u3ySGqCq5Ye61t6fSksVkTw6qMHfL-Q-sy6ZHw9ctOraIGwOUigIBI7RQ3ixaEAWQQkGgChiGb5_ZIUINuH5GAVYr5n_5K7geAJd4quugfU8VybyFeAm8Qzh0temShCgYOnbfc8nGo9q_FD--vThON1JXlELnc-64TJCcoQZheX91lC-GFgtfpWwKTa3FMJ49AHjBWyg4adH9DCGlQvdtUqt4xCYdewdcALKTwsuo8-wn6fy3NwpfTqQiJLI-ncxecqBx4xxQojQXoxNBOcnBRmcB78JLDxIj7YvjVCe8APri8r118JULcXIFXlbvfNijCnk8YKGNqi7IX7X1Y5cVR-K4tQo-_vC3XegUa-egNOi36_Jo_5xCOsSgbWcUAvZkGJulijvQLmMSMxoxojh0cNFccRfSWwWkOwKv84tnTxYHiVJDsiwgcNGL-HnooUVtjLA9R5yhzhLKN5J5GfsqpiWQZAJg6L64I0GOQ9xC4A0WEbtoKMePCLGgheadUDf3h5iJgmXD_jbDnA=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request has two material conflicts: 500 invitations cannot cover 650 guests if each guest must receive one, and individually addressing them requires recipient-specific information or variable printing, which conflicts with using exactly the same text on every copy.\",\"text\":\"Should the order be for 650 invitations, and do you want each invitation individually addressed? If so, please confirm whether recipient names/addresses should be variable-printed or supplied separately; otherwise, clarify what you mean by \u201cindividually addressed\u201d while keeping identical text.\"}", "call_id": "call_eDH551q9MfMltpzk9bCVU808", "id": "fc_0c1d5dd7d637d504006ab36ce783ec87d2a9e4ceb1960dd50a", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request has two material conflicts: 500 invitations cannot cover 650 guests if each guest must receive one, and individually addressing them requires recipient-specific information or variable printing, which conflicts with using exactly the same text on every copy.", "text": "Should the order be for 650 invitations, and do you want each invitation individually addressed? If so, please confirm whether recipient names/addresses should be variable-printed or supplied separately; otherwise, clarify what you mean by \u201cindividually addressed\u201d while keeping identical text."}, "id": "call_eDH551q9MfMltpzk9bCVU808", "type": "tool_call"}</t>
+    <t>[{"id": "rs_01970afda7ee6687006ab487dd7f6087d290b1326b94b985ff", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIfeO3KWbOdBkRAL-UlrJ7XblOkm6Bv4NRXpP4AscxWSRzIA8hSatVWPX-gt3klOWP-DOAHtPK4XmrZQdrLbyjvHWZgxC2uqp2Sf5XnqhVTXgYkn23_7Lh3_W6b7PM08enJ6XuTEX-SqeI1xtbYKMRaRLhc77pTmAxJT6tSIlc3O5HsiODkkYA-e97iPRxe6RpRkuBO_QSMyNhulgrnAO3u_prWrrUMiS46btTeFgC9bebvWrdZihED0y-IvsYIqJnw2BsFqq9nBCOFVTbP-LK80Pzh8MZT2LJ8ivuVQDDBCqrxPywXcXWVe1pgHmsXKgBz1NZY1Qg1_eHdrD4WlHotQl0-aSKvAmzCzA4tdMGbEas7vcyNH1uwBCLV89HW645K7iiZcb_AtL4qYoSM2JDXkzMCapee_mOIllJ9aMwksTIqK0jnn-W7RB41hrK614QyRTS9JEIKPgNRJsxNlR2Ss-FHCy3Xmzw4Vb1_mXfIwjAOZMMxbOwlUzFNzW6aT0NQ-jvzMjDXzKbK2Kg9BcCtpr-3PwtTzfgDfThutYGGqX2Na2pIF3j-yShXGn9m12yOq-EeeXNY8UjS6R7pUGUWCWVY8V0n3ioGHLvL8bXH7gUZWv38-RCuI_AHrAeEyhaar6DEC3GPFw-QixLXMFmlSixk3SXGnw1cIhu7uBwSPHZvl_DShWq4AxTEy-9rg_0jnITJJOfO2GXxDqOELWvUOfa3fKQh59l-8ztJR1MWPpx9dvOBiIemLV3zRynj1oYYEzPmbrElJbSdonANXIhuekaQnETih08iQwpuL4YR8odjAV8GAuE_-SZD1JNCy4r8z6SJ6lSLIuQ8epikCjC06XCeDj9FlA_nmLluR3E0Nb-PmnQkAMvAu6fftWntBbukrqdOqLk7koso0JavsUVwPPjK7VmNxI4MzARtJc5qfwEg7viIQ0SB196MwM4LyKPS7-ghcqPU7bR4SF3R17c22Ok1R-5vMimpEqt6K2jddZpuTHAPonSqfYJafr2WSKExfVB5zfQ7FUwtRj-A_6EyVjB0DgtwLH54RKIFGspgHy6CGuCaRqEvTwq5TuwBk9xtyyWnFWRruPQk1dcTSSg6FdSqoAL3RQwgGukNEq4NC-VSiDbjli1THaBaKXN7lEjv3IQjCkS2Ot8ffJs6JSFJgtHg5Fm9yiLwFnPnIlhVomODU85DnIqel4kPRZB3NJx-xLkE48zF5uDfbQUGokeEc1aE8cQxOlDHhP4UpKHYDQ2_FTqADy9tR5XDgFxNCcYjZSb-4xBc_vx4Hgd_8EirJoefHS1pVTy0WigfDR9PRgKR7g9hHaF3uf1n72ff_YUhZ2xQx0ixllmauZC2J76Qhz5IRrz1K6JTJHoKXvzz9DU7mI3IbiVs7R-db4SAPIZds5qIhXk1-cnOv29Ba2myqj1t5ls7rcT8ojvdauwSMIi4cQDeW41ZC3j2elvkLfWlu6YUYRbTnkBE-uUAClM2-jY-0gMOwBJmUYma-adHAOYjldiQCkzcYQ7naua-9Om0C_kazC2Ut9OnTlfDUS47ZeoXyxjedkjbFTsRBlZV9gpIfQInZoJAq42CAcTKxvLPt"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request contains two material scope conflicts: it specifies 500 invitations but 650 guests who must each receive one, and it asks for individually addressed pieces while also requiring identical text with no variable printing.\",\"text\":\"Should the quantity be 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all 650 printed invitations have identical content with your office handling all addressing and mailing?\"}", "call_id": "call_az0rpqrY0qTXBQFVU5BDuxyg", "id": "fc_01970afda7ee6687006ab487dea7d887d2951d38abc69f89c4", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request contains two material scope conflicts: it specifies 500 invitations but 650 guests who must each receive one, and it asks for individually addressed pieces while also requiring identical text with no variable printing.", "text": "Should the quantity be 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all 650 printed invitations have identical content with your office handling all addressing and mailing?"}, "id": "call_az0rpqrY0qTXBQFVU5BDuxyg", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -373,14 +373,24 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce1-b698-79e0-97be-7b21c9eb79a4</t>
+    <t>01a0d133-118a-7ce3-a1cf-76986af715ce</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>[{"id": "rs_0d864b2ca1e38a23006ab36cfca06487d2ab204b69bb29728c", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2z9j4W3kooN1KD0xKDm5DxsTMZjxAMRaBh5f6FalAwtJltIO2yqm0jz8SmQgXdda88jZvVm9eUETmzx1piCS_yZ_v646N7RwciPiD5Q1dB-dZxrOEqTcZia9-_weSDsVgc5Fs6xWuyIYxIzXIGTsyYaBeUhwJvXJv6XelcW4eLgm_OQq5OjEt4-d5pY5iSdX1CpWXb9302YMa0PLHNiyXiqbSpY6u6wBjhVgMj9eTYlcDVAIdY9juHuTsCy0hiqEGqyU-49dijf6OIbslmGus2VUFEdVKSlLlgkxd2ZsNLBwgPMebZ75Wv2YFpF35vrtFh14XEa0wG_kpBjwmMHbq7Q-KTNThrPtO0zASTCNfKb4UEm0nhFBKlcEHd4CHJ_jQ1j1cJU82bLHUEjYKTVWRrNJjyxkrUDdkRnFn6r-srUxKHiSl3zuo0ni34T2ZP_bVxTR3DIrXAfq1_Uu67hZ9VeC0YLlZj4yMkyD8Mawab2gE0RroBBiqHKMrjWLAxMjP2uNH7XTZJSqJDhhql0XlO_B3l_ShyPW2CxPO1CmnO2i5Dgifc1ahi9soBra5_ZKEKobBnYsLsODMATF4hzUg5DG_dLBhCSo3wevSBXexcrCzDpU6nGHGXX_x8MtfsVUZRrOufKFi2vR65QbnLzxv3jrfZkOMNUQ6j8sGQVz3y_ZgvoPTtE0Awsxqw75DTrhV6PTFSCHJKbXG5mlphX4hpQi3T5i-h37t00hvq9fKE65radOk5dfQXdWDytWiapH0S5tjSKURXI6wTODnoLn5r0B1_2F7Mj3Hw09rYa5gzTJ6f8ZWZpjMwmTdO2xrDJj1eNsLAKVPbJdvMFtjBRrZjvCWh9dxMYpnajCg6Eew2bWQ0GoDU2nOewj8rcLtQkNKY11nwk6JcduAgyWA-YJ_xX7uhZ0cXvLutoErj7SHI8C1Zcbjo5kyN5MpER-JudM1Wv1hkxzmxF697nSU-oc8IuZoc9zOVtIJT1hQgfnKObOw3AMLMjBZOLTUS2S6-ZHoFIiD6qLoMKf-3WFt8dAWptunH8f1upSICzTGBECPFd0seqXsVuafCIL7CGWhlk7PJyBKT9dXoBT4T3TP1i_SE-6MXyq6Qt4NvFW-saMMbEuXZsDu9o2BXSFdqlOGIDcBnqksxwk6c7ZJSS0M1f2MENW_qOiCoDCV7zzsvO6kPG3yu1c6cYhCupaEes9mmtF5_fCoW36bLiz0w2GULrTksilBU8_23zjLC8k6nEJfA0Bx3YV11PSWGcjnq4DLpgYatFZCCemupzReNmFizOR1TaGpBF4SuOxgW3wz1IdFAzPClVDTgtNE9aH7w75YqeurSAZ1QKb3cYdfTPgt1-12xnjQ47pYo1p4XPClrQv1dOyR_mVHoGsTd0yBvgwf4Xb5GjaFgaVIKovQdGnA8YucbFe2ZEfWgVJQsLyiMbCuf6AEoZw8aIa-B5R6KwBSpWDzaVMcF7CYiQ31j-NImgNuKISdweTLmKjMcUsjipIniTOYNJ9ISZ3CtRe970zhE-HxwqPQ1PMx0VrK-tp6d59VMQUE91hy7DrxqrjcZo0jy98CKEjFa715WijapnbyCMxiev"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"complete\",\"reason\":\"The quantity and recipient scope are reconciled: 500 households among 650 guests, with one invitation per household. The invitation text is identical, and the household names and addresses will be printed on 500 envelopes using the customer's spreadsheet. Delivery and mailing responsibility are also clear.\",\"text\":\"Prepare a quote for 500 identical-text invitations and 500 envelopes, with each household's supplied name and address printed on its envelope. The customer will provide the spreadsheet, receive the complete order in one batch at their office, and handle mailing themselves.\"}", "call_id": "call_iV4eY6YTKofFQcS5UldKUg6W", "id": "fc_0d864b2ca1e38a23006ab36cfdfebc87d292aaf5c2ec7395e3", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "complete", "reason": "The quantity and recipient scope are reconciled: 500 households among 650 guests, with one invitation per household. The invitation text is identical, and the household names and addresses will be printed on 500 envelopes using the customer's spreadsheet. Delivery and mailing responsibility are also clear.", "text": "Prepare a quote for 500 identical-text invitations and 500 envelopes, with each household's supplied name and address printed on its envelope. The customer will provide the spreadsheet, receive the complete order in one batch at their office, and handle mailing themselves."}, "id": "call_iV4eY6YTKofFQcS5UldKUg6W", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0a7e38912863ce39006ab487f500a487d29fc0a39c06c94d65", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIf4hgNhLoT9OZru5REcX-pIxfrRw0fVUb_GeNBBzJ4SDZEVdnV-xodhbRl9AcfhG-Zq9xqUPpULTGxdzD5SZ4-uwXQ_T45ymrvnmyyvE7XYPL-_M3Myvsu9hT6n55-hQ9lgi--r17R8qHoydqjMdykdykCTgf1G61uzceFo_dZIMYsuQ92rBHq9Apdnxei_Q5rHo_ZAgxnhFwCb206b5hobit9_WxdLoF38untW8-DXRBCFIBkT1hAvQ6tSE3qKXcrMd5pjHp_1jvpfuLx3KJ_gTPrGrwI6JB5xvg-aNzBx1oST3HrBiby9Q2wTYApmJKw2_V4M5Mhw51srAYB2KdRYXYBLMTnKFQWGMzIWPpQLXG37T5RbQ8LO8Tjh_kJRBfwvI4hPJ193O1tuveQa7RPGW2MHcquBPpGuXD5wLsdmsGkhtP3wqcirBTU5zsC5HyZXwQtnIuiaOB2lyaxpAXs7qHmt2L61tT5jEea3SQObJpkuamD4aOpyZVDh5hlkbDcY7pjVVLHETDgxiX-DeCMEQgYWc9kC0UgqMesouz6s7Mycg6apGGyRcUbNpFXw9O-1rk9_JSWmAuukqjwd1V0JYIXfKJ4OUCKYX38V18dBKLd3g_gsL_s3kc7sXD-gtxtVgfJbBAihN6s_zxgcR68j2v-DetUwAlg7vzBlhD1zDklxwBnjGFdexE2m5mAWG4lNyZG5JwmXWdFA0nLVCu7IKgyDJXu2TQ3UqJmwoNhAQjWqx3sRD9WkVkt8ovkDtjPwXbNGiqdBBquHdggWwxMM9mYzVs3y1OnDO5pDu8YX87FPGpY4A24-x7YQ06o5DxbEIr_U8r72MQRZEs1NC1wgpOe_IlsPu1XzgVIFILv8IjczT_U0ejkGwlcnN581IWeVjTO6D29VNx8DOx4Hd22tisW_HjvRd9AAXfQ_PRJMKvVjhf-MV2NpiqVGTgud83fO2H6v5n3K11fDuODcJYdU5p7n_A2RZvqKaqII58z_n9PFTaQSQKuiOmGFeUMpFMuxuFwCmNAVrSgpYNx74U_lCwIWeKCtM_VNdRA3q2hundjzeR6lIhRVticxdhQ27maWhl7U7UJaxLMyWyuXxLdy00UkQz6lnzKEVzpBq_vhNr8BSifouNdZJBm8fLzTB5FDCr650uLxNd-T_ftmJ2ZDi_l1wYecKEry2_9kCeJRv-odOGX2urqc9s5kfcrDHYRWu_TxNkfu7kQufBcHRvTZMasiN8_YJl77Z6QLoubxEbOAsrKgGD0hv0I0rPzsvvU67dtD20fhXwDPr4Gnxf0gm5ETegl07N8m1VW94pqCxRbVY1SjY3O78fkRKPkp6StzQgCPpWs4iARGFXU1VBOX03f5fM8UzYLAdUx4ldoPnJpttwiYPDJPiTfs76tC1zhBo8iCe4zqsj2_rIicRIhFaS1_OR4_ykn0OqIl6ty_mUTfJs-HfLvvR4YmM3mEnnp2TRmN9P_YbwFDjHBxaKi_OqbWjB42PxBCEulliNxcNMHw1MSLBSrskehLaShL60awDA_cJb2mZIAoOsQXiCXmR2CJFHWvbmvO2mYFz8WIp7OtnuB5obacvTIhpC-rZ_vJbqc9szTVXxV-l77XsBaEVB83G9sThqFCLJtZzhMIeQQOVjgKA7ozh58_K7kHrk2_-Rjn307ask1NUFZkxiAXLFxzBf2L-rLbBjjhfbdvfCm2cNtUlEqnGwteQ6H4HT8WV9PLxyVm8eR7Zv8ukJkTqVcUGTbWBvmgGtsinsOXs-T69Q0gNJ7HpOyXG7uKlCb9vjrntZF9tdjbKAjF8o9PnY5e-xdZf-X4LbPIFMx_ySHDeD7v1EiCl57XqmfFmCAJIWGOkQNrVkaHcgGrc_aZgajVFq3Vyd3rixB9-IvJ-DBfjeMu1JxEpHxbNcCTguOBJm4RK1sPub4JxEzMlRwpbGEFk72iNKidu5uc2ybr8XKRI6MH9e4r8zSXTg822zby_XH2v0njI0NPuE2ygiY6vodtFf_NDZ49azIUnWFeFF1ApK00O0oW_X7pw2Fc5x4c0klBXySLfBzH1cJsv156YnbKjPIO4J-PnWVTkbogCAEUJ2lKUzFA1Yq6e_KPgdjI95wlFZKTAJ8xw7hk44cT_PK8OFHKt5y1uXrqh9aFu1KWQcDdn0WNaJ9y_4H9wAtk9GN7HJJvYyZtQDkIdk23EcQy3fLQxDIEfGeg-j1pWObTEmqd9Y78noDWjtVpgILsnZa67_y3MvASfDCRDgTiEYELDxiOhkx_FHMS1QNHL8d3_EqIaKWcz6XV1UQkmdxiSprgXX15zTgmTGITQJ85IWKwHytLc4ZDiwYptUkgxt5OXAy5JTfteZL3_RSqo3mcBg_wMo-UOD1XmGOgczu1N91LJo9XjE00Lt0a5kf3yu547wdtrUnpm6NMue4WxFu4tKCVKzdqVYyg5o-Fe4OArT3ziETkx6gA11g5CWljsawsgdL2u8Ouem_1SE781Bo_bSb2qCSUb5e7-cnoxdhJfKFwhwzeBAsTCXoIkgyUdsxecikvMHiLPTyWfSuqEzkpozB_Xu6uMxUHD3jG9DBMgQ=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The quantity and addressing scope are now consistent: 500 household invitations, each with identical text, plus 500 envelopes addressed from the supplied spreadsheet. However, it is unclear whether the printer should assemble the pieces by inserting each invitation into its corresponding addressed envelope (and, if so, seal them), or deliver the invitations and addressed envelopes separately.\",\"text\":\"Should the printer insert each invitation into its matching addressed envelope and seal/assemble the 500 pieces, or should the invitations and addressed envelopes be delivered separately for your office to assemble?\"}", "call_id": "call_DQ45b1X9ULyLlOEg0TYixrZh", "id": "fc_0a7e38912863ce39006ab487f8560487d288cfa0b10851cfa1", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The quantity and addressing scope are now consistent: 500 household invitations, each with identical text, plus 500 envelopes addressed from the supplied spreadsheet. However, it is unclear whether the printer should assemble the pieces by inserting each invitation into its corresponding addressed envelope (and, if so, seal them), or deliver the invitations and addressed envelopes separately.", "text": "Should the printer insert each invitation into its matching addressed envelope and seal/assemble the 500 pieces, or should the invitations and addressed envelopes be delivered separately for your office to assemble?"}, "id": "call_DQ45b1X9ULyLlOEg0TYixrZh", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a0d133-a99c-7e60-8aea-8333e658ca6a</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0a2c09f56a55c5db006ab4881c7a8487d28449fbe438a7f063", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIgeuA24LoKv2SpEH5gg6GH8x-b8bAffq_NCjlyJQxbVJkVy_TEV7v6Ov9NWCsHjCze6jgVrJ4nHeH92ximm_F5NJNFq9S8rdO_XqUYQqrvudrulGF6K7Fcnqk12ep8J5-IiiWDzzUydhWZQUE-o4x_UxZzCBpL_g2NcV90hb1fggPK7DAMIr8b0FYd85S42BXdrQuXoz1mKVmau_FKaP1eQYUFDlbhhD6vC1d3rp5IK8hTM8QrrESwfAjQrWm9viaWnlnj2fXuk2GcKm6zqxziDP5VXuD2cqOjYEcAENbm5E_L9D0YqIEP5MLpe6SzYalHkaAHugtMLp8I4hlwo4rYy7Su8Q_M7nuIAkTE3I-96G7WhoE3lCXztXOSMWEd3SPN2SUSp08g0TWVM4xZrZ9sceiVeolzfSqNHgS8E_WXE-2YjtIoKkmg0JyxMWNWTbHDas9XIejSeHO9ipL7FGcn1k257izjXPotPl4AVb_30EnUbTm72J11EBtPfaQ5QZSGBJGFvG9bPdGlM7btEUjg5ILDL7vRUD5w4CSU7ZPywcl4AYtZ9cyQctQDm4yoL6G53o9631eR-ALXfG9DRgUxn082FbKZ2sVEHJ6B6_oqVtMyVgX0HqkVAq4NOlFaIdMVQZQLpA3Jyq0RqVfrQcZuY9ANw0MVLSbuynIn39UPboCfQfVS2f9NnptcsLRfaEK42zwUt0CgT33dpecYbHQn0OWGIW2ncRpzcW307BURZUCuWsTinTpOFLj4ppX3kzQcpWd7zgGvibG4e_p8vf2RHyJ0Ef1gHtTTpkMPYKX5ZWdI0sPspnstzK3UyRFp-D_b1T3ltIF6pou_Z2Q3fd4wr3eGh7ReTET0OZaPbLBIcWIGcZfcK8d40FxFQVZZ12RL3EawfTntKxpFhi1sNqmsEvssLLmFGPku4Cp3KCBdaGtIAfoFG8SSwmlPm-VZAJ-doc0nXXD6BZBVKluehwgw1nyZkIU0So8dopy-xacVtjYwIm_Vk0HaLbkzG8Ygz13Ta7VTOvbIekfqkXZleb7I88hI5cHkr28qYuEY83qsDSqgLlMJ8EhAHy4FjFYCMqpOEHK2L6Z0M8m1x0Qm91trIi6cViAU21stQT9wOLr6GrSG79H3qRCQDS_1OwQLoyHC1PNeZJwdcPTvYu7sDQX2fWyjBAgdXO6H5xldO2wuGPxfnDyCZvwiNmLxz3obNqyu3X5pxzbeHlFfiz9YwukzhiwMY5pY5X4eu1KwIumpY5bQt_C0bTnY9vEnHVNVOHVMjK04YDdRS1U8Shuwwh3aMF1y96qwnGz95OBNQH6LzHgJOnfrD2Hc-6pPUEr0GD6h0JImkT8H_3sQ94udDf1MKkBDeDoVXy8ffnSHQGTx9UtLQnp_rTF0H7k9Oil-ClH2fUc4Mg4D58jH-RncClGukYE_xqnJpIDiPEl5CugAslg5Pzv_mPT6Hefse5PrVkGpUqmwcMunXBAlNATUK-yOLCYUJ6qP36e6VgKrIQDxk3ZxIHjP4e5BNCrD_Y-aN49eT7YzHyJX-A58q3IoitR9OqSwz213UcD28DjpBQmwUyM18y35PhcRpPiiKFjyB_zyh3ungUXFLeD04_jCL0vMy_fl1RA1Bf6aa-KuhujulcjKvxAgPMoQ97Ktw-Mzj_u7YD94yqN0bw4aq7s1uHFkz9-lc5Niz6puWvB2Q3fbw30lZQrMx_o9zKtj9bEOb5zKab1YMCM3MtoIM_CoEU8tnQO5x2NE_UMVDGeuFgBS02KsLUs_Vv7Jef3UWUEgK_4_GjMffuNokwM9SDXpPZ-Fc6pu2Fg0Fh3Xb_g3CbHLIZuFNOPb5giQdUPnHMm5Di3lUASuUBOAIxoPVeorGPmbQEWH8V0uWJIQB4_NBIzTUpJZ-KqclCUKA5jPeN_I9r6xp"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The quantity and addressing method are clear: 500 identical invitations, one per household, with 500 addressed envelopes for 650 guests. However, it is still unclear whether the printer should insert each invitation into its matching envelope (and possibly seal them) or deliver the invitations and addressed envelopes separately for your office to assemble before mailing.\",\"text\":\"Should the printer deliver 500 invitations and 500 addressed envelopes separately, or insert each invitation into its matching envelope (and seal them) before sending the batch to your office?\"}", "call_id": "call_5bIEcg65zxEWxporkThfN2EP", "id": "fc_0a2c09f56a55c5db006ab4881e329487d2a40a9c9d6e7d471d", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The quantity and addressing method are clear: 500 identical invitations, one per household, with 500 addressed envelopes for 650 guests. However, it is still unclear whether the printer should insert each invitation into its matching envelope (and possibly seal them) or deliver the invitations and addressed envelopes separately for your office to assemble before mailing.", "text": "Should the printer deliver 500 invitations and 500 addressed envelopes separately, or insert each invitation into its matching envelope (and seal them) before sending the batch to your office?"}, "id": "call_5bIEcg65zxEWxporkThfN2EP", "type": "tool_call"}</t>
   </si>
   <si>
     <t>LangGraph</t>
@@ -401,7 +411,7 @@
     <t>Execute the begin workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce1-6169-71e2-8aab-9e6bd4736ee5</t>
+    <t>01a0d132-b476-7663-a711-a6b17af32faf</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -413,7 +423,7 @@
     <t>Execute the assess workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce1-616b-7b12-a39a-e8bc1e07d74f</t>
+    <t>01a0d132-b478-7dc2-ba3f-c8229bf4d00f</t>
   </si>
   <si>
     <t xml:space="preserve">        quote_interpreter</t>
@@ -422,19 +432,19 @@
     <t>Interpret quote scope and request human clarification when needed.</t>
   </si>
   <si>
-    <t>01a0cce1-616b-7b12-a39a-e8cddd06482a</t>
+    <t>01a0d132-b478-7dc2-ba3f-c83965587b76</t>
   </si>
   <si>
     <t xml:space="preserve">            quote_interpreter</t>
   </si>
   <si>
-    <t>01a0cce1-616c-7af0-85c8-5eb3499a67ef</t>
+    <t>01a0d132-b479-7172-a853-94c430ea0c22</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cce1-616d-7960-bb2d-64b1a1fe878a</t>
+    <t>01a0d132-b479-7172-a853-94d1a50047c4</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -452,7 +462,7 @@
     <t>Execute the route_after_assessment workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce1-6ff6-7e42-a8f5-334ac65d2743</t>
+    <t>01a0d132-c37a-7e32-983e-5632d71a7d69</t>
   </si>
   <si>
     <t xml:space="preserve">    ask</t>
@@ -464,13 +474,13 @@
     <t>Execute the ask workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce1-6ff8-75b3-9b6b-131ec955b34f</t>
-  </si>
-  <si>
-    <t>01a0cce1-b68f-7c51-8560-adf8e99061cd</t>
-  </si>
-  <si>
-    <t>01a0cce1-b691-72a2-802b-a4c8eaf554cd</t>
+    <t>01a0d132-c37b-7222-8913-854965114e1e</t>
+  </si>
+  <si>
+    <t>01a0d133-117e-7412-a0e6-e01193fa09a8</t>
+  </si>
+  <si>
+    <t>01a0d133-117f-7d83-aa06-63185f83ad93</t>
   </si>
   <si>
     <t xml:space="preserve">        route_after_answer</t>
@@ -479,31 +489,61 @@
     <t>Execute the route_after_answer workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce1-b691-72a2-802b-a4d1becd1d43</t>
-  </si>
-  <si>
-    <t>01a0cce1-b693-70e1-a394-b812adf39488</t>
-  </si>
-  <si>
-    <t>01a0cce1-b693-70e1-a394-b822b4212b7f</t>
-  </si>
-  <si>
-    <t>01a0cce1-b694-7e60-9fb8-2b73f2f4ff4b</t>
-  </si>
-  <si>
-    <t>01a0cce1-b695-74d2-8a78-82541c7a0a82</t>
-  </si>
-  <si>
-    <t>01a0cce1-c7a5-71c3-b636-cc0023379662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    complete</t>
-  </si>
-  <si>
-    <t>Execute the complete workflow operation and pass its result to the next graph step.</t>
-  </si>
-  <si>
-    <t>01a0cce1-c7a6-7622-8620-9e4966d5a5ff</t>
+    <t>01a0d133-1180-7270-866d-0c9dd907bde1</t>
+  </si>
+  <si>
+    <t>01a0d133-1184-7871-b971-e47d33011813</t>
+  </si>
+  <si>
+    <t>01a0d133-1185-7b63-bb1f-e8eefc719b54</t>
+  </si>
+  <si>
+    <t>01a0d133-1186-7842-b2fa-bed9045fbb69</t>
+  </si>
+  <si>
+    <t>01a0d133-1189-7511-974a-d5358dde7c37</t>
+  </si>
+  <si>
+    <t>01a0d133-293b-7c40-b4c1-4ab184998a15</t>
+  </si>
+  <si>
+    <t>01a0d133-293d-7640-b1f5-6d6a5e4cf7fa</t>
+  </si>
+  <si>
+    <t>01a0d133-a990-7020-bcb1-e6bdf0ea3b0c</t>
+  </si>
+  <si>
+    <t>01a0d133-a993-7572-83c9-41bb34523e45</t>
+  </si>
+  <si>
+    <t>01a0d133-a994-7192-af2f-8c42f1fa2726</t>
+  </si>
+  <si>
+    <t>01a0d133-a997-7f12-a380-e6d1a5350a86</t>
+  </si>
+  <si>
+    <t>01a0d133-a998-7eb1-a02c-60bfd6776ae5</t>
+  </si>
+  <si>
+    <t>01a0d133-a99a-75a1-ae01-3125ed1cdf9f</t>
+  </si>
+  <si>
+    <t>01a0d133-a99b-7f83-a110-9f23643bd343</t>
+  </si>
+  <si>
+    <t>01a0d133-bb75-7d21-9e45-fe5f7dc4d9e9</t>
+  </si>
+  <si>
+    <t>01a0d133-bb78-7f83-be1f-0e66998fc57b</t>
+  </si>
+  <si>
+    <t>01a0d134-1e7b-72a0-a391-742e647aa97d</t>
+  </si>
+  <si>
+    <t>01a0d134-1e7e-7a73-b27e-6a89544ed930</t>
+  </si>
+  <si>
+    <t>01a0d134-1e7f-7ae1-a52d-3808669adb78</t>
   </si>
 </sst>
 </file>
@@ -910,7 +950,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -970,20 +1010,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
-        <v>0.000589373172</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
+        <v>0.0010603835</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
-        <v>0.0006756</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
+        <v>0.00121</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>106.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -994,20 +1034,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
-        <v>0.000589373172</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
+        <v>0.0010603835</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
-        <v>0.0006756</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
+        <v>0.00121</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>106.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1045,7 +1085,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1132,7 +1172,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1146,15 +1186,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1176,23 +1216,23 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409" customHeight="1">
@@ -1243,19 +1283,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1272,7 +1312,7 @@
         <v>94</v>
       </c>
       <c r="D18" s="4">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>95</v>
@@ -1322,15 +1362,15 @@
         <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="F20" s="2">
         <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B17),D20*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1374,7 +1414,7 @@
         <v>105</v>
       </c>
       <c r="D23" s="4">
-        <v>194</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
@@ -1388,23 +1428,23 @@
         <v>106</v>
       </c>
       <c r="D24" s="5">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="E24" s="2">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="F24" s="2">
         <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!F17),D24*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="G24" s="5">
         <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>19.0</v>
       </c>
       <c r="H24" s="5">
         <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
@@ -1418,15 +1458,15 @@
         <v>107</v>
       </c>
       <c r="D25" s="5">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E25" s="2">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="F25" s="2">
         <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E17),D25*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="G25" s="5">
         <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1485,26 +1525,268 @@
       </c>
       <c r="E29" s="2">
         <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25)=4,SUM('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="F29" s="2">
         <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25)=4,SUM('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>111</v>
       </c>
     </row>
+    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="4">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="4">
+        <v>662</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="24" customHeight="1">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!C17),D31*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="24" customHeight="1">
+      <c r="A32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="5">
+        <v>662</v>
+      </c>
+      <c r="E32" s="2">
+        <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="F32" s="2">
+        <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!B17),D32*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="24" customHeight="1">
+      <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="24" customHeight="1">
+      <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="4">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="24" customHeight="1">
+      <c r="A36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="5">
+        <v>100</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!F17),D36*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>0.00012</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="24" customHeight="1">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="5">
+        <v>127</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!E17),D37*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="409" customHeight="1">
+      <c r="A38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="24" customHeight="1">
+      <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="24" customHeight="1">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="2">
+        <f>IF(COUNT('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37)=4,SUM('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="F41" s="2">
+        <f>IF(COUNT('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37)=4,SUM('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="H41" s="5">
+        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE29">
+  <conditionalFormatting sqref="A2:AE41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1518,7 +1800,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE20"/>
+  <dimension ref="A1:AE33"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1625,13 +1907,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -1640,7 +1922,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -1651,7 +1933,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1677,60 +1959,60 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>3729.158</v>
+        <v>3847.202</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -1739,30 +2021,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.519</v>
+        <v>0.405</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -1771,10 +2053,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -1785,7 +2067,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1811,60 +2093,60 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>3724.375</v>
+        <v>3843.273</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>47</v>
@@ -1873,13 +2155,13 @@
         <v>111</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" t="s">
         <v>129</v>
-      </c>
-      <c r="I5" t="s">
-        <v>126</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -1887,7 +2169,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1913,60 +2195,60 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>3721.981</v>
+        <v>3841.727</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -1975,13 +2257,13 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J6" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -1989,7 +2271,7 @@
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2015,60 +2297,60 @@
       </c>
       <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V6" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W6" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X6" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3720.672</v>
+        <v>3840.677</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -2077,13 +2359,13 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J7" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2091,7 +2373,7 @@
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2117,60 +2399,60 @@
       </c>
       <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3718.433</v>
+        <v>3838.793</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>95</v>
@@ -2182,13 +2464,13 @@
         <v>493</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H8" t="s">
         <v>96</v>
       </c>
       <c r="I8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2196,7 +2478,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.6015682e-05</v>
+        <v>8.640811e-05</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2222,63 +2504,63 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>127.0</v>
+        <v>116.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.000132949188</v>
+        <v>0.00012198792</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001524</v>
+        <v>0.0001392</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.414882e-05</v>
       </c>
       <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.32e-05</v>
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000277588134</v>
+        <v>0.00027254485</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0003182</v>
+        <v>0.000311</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD8" s="1">
-        <v>3716.362</v>
+        <v>3837.028</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -2287,62 +2569,62 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.302</v>
+      </c>
+      <c r="AE9" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0.337</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.405</v>
+        <v>0.457</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -2351,22 +2633,22 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J11" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M11" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2391,60 +2673,60 @@
       </c>
       <c r="S11" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T11" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U11" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V11" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W11" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X11" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y11" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z11" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>4376.078</v>
+        <v>6080.118</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -2453,30 +2735,30 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AD12" s="1">
-        <v>1.455</v>
+        <v>3.092</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>47</v>
@@ -2485,30 +2767,30 @@
         <v>111</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" t="s">
         <v>148</v>
       </c>
-      <c r="I13" t="s">
-        <v>145</v>
-      </c>
       <c r="AD13" s="1">
-        <v>0.299</v>
+        <v>1.142</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -2517,25 +2799,25 @@
         <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J14" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2560,60 +2842,60 @@
       </c>
       <c r="S14" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T14" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U14" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V14" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W14" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X14" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>4370.533</v>
+        <v>6072.375</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -2622,25 +2904,25 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J15" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2665,60 +2947,60 @@
       </c>
       <c r="S15" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T15" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U15" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V15" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W15" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X15" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>4369.011</v>
+        <v>6070.035</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -2727,25 +3009,25 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J16" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K16" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L16" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2770,60 +3052,60 @@
       </c>
       <c r="S16" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T16" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U16" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V16" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W16" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X16" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y16" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z16" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>4367.631</v>
+        <v>6067.659</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B17" s="1">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -2832,25 +3114,25 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J17" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K17" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L17" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M17" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2875,60 +3157,60 @@
       </c>
       <c r="S17" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T17" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U17" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V17" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W17" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X17" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y17" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z17" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>4365.756</v>
+        <v>6064.297</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>95</v>
@@ -2937,28 +3219,28 @@
         <v>111</v>
       </c>
       <c r="F18" s="1">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
         <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J18" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>623.0</v>
+        <v>605.0</v>
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.000108697302</v>
+        <v>0.00010603835</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.0001246</v>
+        <v>0.000121</v>
       </c>
       <c r="M18" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2983,63 +3265,63 @@
       </c>
       <c r="S18" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.0001367106</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.000156</v>
       </c>
       <c r="V18" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>63.0</v>
+        <v>181.0</v>
       </c>
       <c r="W18" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>6.5951172e-05</v>
+        <v>0.00019034322</v>
       </c>
       <c r="X18" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>7.56e-05</v>
+        <v>0.0002172</v>
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000311785038</v>
+        <v>0.00043309217</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0003574</v>
+        <v>0.0004942</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>49.0</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>112</v>
       </c>
       <c r="AD18" s="1">
-        <v>4362.213</v>
+        <v>6061.903</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -3048,55 +3330,909 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.348</v>
+        <v>0.465</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>0.538</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="54" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="G21" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K21" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L21" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M21" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T21" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U21" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V21" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W21" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X21" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y21" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z21" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA21" s="5">
+        <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB21" s="5">
+        <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>4584.89</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="54" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>2.44</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="54" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" t="s">
+        <v>160</v>
+      </c>
+      <c r="I23" t="s">
+        <v>159</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="54" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K24" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L24" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M24" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T24" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U24" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V24" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W24" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X24" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y24" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z24" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA24" s="5">
+        <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB24" s="5">
+        <f>IF(ISNUMBER(Z24),ROUND(Z24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>4574.805</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="54" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K25" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L25" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M25" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T25" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U25" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V25" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W25" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X25" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y25" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z25" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA25" s="5">
+        <f>IF(ISNUMBER(Y25),ROUND(Y25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB25" s="5">
+        <f>IF(ISNUMBER(Z25),ROUND(Z25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>4571.756</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="54" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" t="s">
+        <v>163</v>
+      </c>
+      <c r="I26" t="s">
+        <v>162</v>
+      </c>
+      <c r="J26" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K26" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L26" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M26" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T26" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U26" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V26" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W26" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X26" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y26" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z26" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA26" s="5">
+        <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB26" s="5">
+        <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>4569.265</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="54" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" t="s">
+        <v>164</v>
+      </c>
+      <c r="I27" t="s">
+        <v>163</v>
+      </c>
+      <c r="J27" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K27" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L27" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M27" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T27" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U27" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V27" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W27" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X27" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y27" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z27" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA27" s="5">
+        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB27" s="5">
+        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>4566.051</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="54" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="1">
+        <v>662</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J28" s="2">
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>662.0</v>
+      </c>
+      <c r="K28" s="2">
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.00011602874</v>
+      </c>
+      <c r="L28" s="2">
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.0001324</v>
+      </c>
+      <c r="M28" s="2">
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>127.0</v>
+      </c>
+      <c r="T28" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>0.00013355574</v>
+      </c>
+      <c r="U28" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>0.0001524</v>
+      </c>
+      <c r="V28" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>100.0</v>
+      </c>
+      <c r="W28" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>0.000105162</v>
+      </c>
+      <c r="X28" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>0.00012</v>
+      </c>
+      <c r="Y28" s="2">
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>0.00035474648</v>
+      </c>
+      <c r="Z28" s="2">
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>0.0004048</v>
+      </c>
+      <c r="AA28" s="5">
+        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AB28" s="5">
+        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>4563.701</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="54" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" t="s">
+        <v>165</v>
+      </c>
+      <c r="I29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD29" s="1">
+        <v>0.597</v>
+      </c>
+      <c r="AE29" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="54" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AD20" s="1">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="AE20" s="1" t="s">
-        <v>123</v>
+      <c r="G30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>0.758</v>
+      </c>
+      <c r="AE30" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" ht="54" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>5.252</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" ht="54" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H32" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>2.306</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="54" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>0.487</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE20">
+  <conditionalFormatting sqref="A2:AE33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -3147,7 +4283,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/quote_request/report.xlsx
+++ b/reports/quote_request/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="157">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d132-b474-79e2-bebb-1d3cde2984ea</t>
+    <t>01a0d586-29a9-7c20-a6bd-7c96a4fb8a80</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d132-b47a-7da0-b744-558a9097def7</t>
+    <t>01a0d586-29b1-7463-a700-fe4f009e7f59</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -360,8 +360,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_01970afda7ee6687006ab487dd7f6087d290b1326b94b985ff", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIfeO3KWbOdBkRAL-UlrJ7XblOkm6Bv4NRXpP4AscxWSRzIA8hSatVWPX-gt3klOWP-DOAHtPK4XmrZQdrLbyjvHWZgxC2uqp2Sf5XnqhVTXgYkn23_7Lh3_W6b7PM08enJ6XuTEX-SqeI1xtbYKMRaRLhc77pTmAxJT6tSIlc3O5HsiODkkYA-e97iPRxe6RpRkuBO_QSMyNhulgrnAO3u_prWrrUMiS46btTeFgC9bebvWrdZihED0y-IvsYIqJnw2BsFqq9nBCOFVTbP-LK80Pzh8MZT2LJ8ivuVQDDBCqrxPywXcXWVe1pgHmsXKgBz1NZY1Qg1_eHdrD4WlHotQl0-aSKvAmzCzA4tdMGbEas7vcyNH1uwBCLV89HW645K7iiZcb_AtL4qYoSM2JDXkzMCapee_mOIllJ9aMwksTIqK0jnn-W7RB41hrK614QyRTS9JEIKPgNRJsxNlR2Ss-FHCy3Xmzw4Vb1_mXfIwjAOZMMxbOwlUzFNzW6aT0NQ-jvzMjDXzKbK2Kg9BcCtpr-3PwtTzfgDfThutYGGqX2Na2pIF3j-yShXGn9m12yOq-EeeXNY8UjS6R7pUGUWCWVY8V0n3ioGHLvL8bXH7gUZWv38-RCuI_AHrAeEyhaar6DEC3GPFw-QixLXMFmlSixk3SXGnw1cIhu7uBwSPHZvl_DShWq4AxTEy-9rg_0jnITJJOfO2GXxDqOELWvUOfa3fKQh59l-8ztJR1MWPpx9dvOBiIemLV3zRynj1oYYEzPmbrElJbSdonANXIhuekaQnETih08iQwpuL4YR8odjAV8GAuE_-SZD1JNCy4r8z6SJ6lSLIuQ8epikCjC06XCeDj9FlA_nmLluR3E0Nb-PmnQkAMvAu6fftWntBbukrqdOqLk7koso0JavsUVwPPjK7VmNxI4MzARtJc5qfwEg7viIQ0SB196MwM4LyKPS7-ghcqPU7bR4SF3R17c22Ok1R-5vMimpEqt6K2jddZpuTHAPonSqfYJafr2WSKExfVB5zfQ7FUwtRj-A_6EyVjB0DgtwLH54RKIFGspgHy6CGuCaRqEvTwq5TuwBk9xtyyWnFWRruPQk1dcTSSg6FdSqoAL3RQwgGukNEq4NC-VSiDbjli1THaBaKXN7lEjv3IQjCkS2Ot8ffJs6JSFJgtHg5Fm9yiLwFnPnIlhVomODU85DnIqel4kPRZB3NJx-xLkE48zF5uDfbQUGokeEc1aE8cQxOlDHhP4UpKHYDQ2_FTqADy9tR5XDgFxNCcYjZSb-4xBc_vx4Hgd_8EirJoefHS1pVTy0WigfDR9PRgKR7g9hHaF3uf1n72ff_YUhZ2xQx0ixllmauZC2J76Qhz5IRrz1K6JTJHoKXvzz9DU7mI3IbiVs7R-db4SAPIZds5qIhXk1-cnOv29Ba2myqj1t5ls7rcT8ojvdauwSMIi4cQDeW41ZC3j2elvkLfWlu6YUYRbTnkBE-uUAClM2-jY-0gMOwBJmUYma-adHAOYjldiQCkzcYQ7naua-9Om0C_kazC2Ut9OnTlfDUS47ZeoXyxjedkjbFTsRBlZV9gpIfQInZoJAq42CAcTKxvLPt"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request contains two material scope conflicts: it specifies 500 invitations but 650 guests who must each receive one, and it asks for individually addressed pieces while also requiring identical text with no variable printing.\",\"text\":\"Should the quantity be 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all 650 printed invitations have identical content with your office handling all addressing and mailing?\"}", "call_id": "call_az0rpqrY0qTXBQFVU5BDuxyg", "id": "fc_01970afda7ee6687006ab487dea7d887d2951d38abc69f89c4", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request contains two material scope conflicts: it specifies 500 invitations but 650 guests who must each receive one, and it asks for individually addressed pieces while also requiring identical text with no variable printing.", "text": "Should the quantity be 650 invitations (one per guest) or 500? Also, do you want the printer to add each guest\u2019s address/name, or should all 650 printed invitations have identical content with your office handling all addressing and mailing?"}, "id": "call_az0rpqrY0qTXBQFVU5BDuxyg", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0795837696be5b5c006ab5a35f689887d2b3d3061601afff98", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaNgNdwz4f5TbCIRlK_E2zLD-kTbjeArpX34VE7wzTwg4tIEMEhn62MAK5SoP_twyxBWDFJ2WRZTQhJQCFt8jbiSYwGPkUqFVICY2Iwf7aXxlqmQc1i9cBxJXqoC0e66iM68czIVjdeCzK7Nzx2QW9L6mmOuT2bgDAfRws4EywQs_BuZhnWe0pmbi7deze3WGw1mHeDB1jPt0_Ph_OhgXv8YrbBgC_CJb88bB3nwc0JUh_xSmnyh7zi3Hu3wVws43viYkWkHqdLUETvV1zGVeqS1Fzw-L4Wpvb23oN1O_VI0pqqvAO8MpH-jfqfSKyfa0LCxZx0ixpJ_nv8ys5hRa9EcPXG1WeRaA-1aJbSqAxrDoZ8GzzGmxV1J2tunYKuJaSVITf236XBoudNFkBR7T9M_Md-AyX-3lljWS9U0vpB0MtPnZvbdmE2cEDIpR0UqaVS2OCAZbmvQ_3YcYDJR3BcOT7Eynoqr1EbqSm8jfmLU3lcZxrHQfmD1vX_YDHK-bSGjP9ZBf9rS7hB0r_blZp7LlYXFo03GOcWAzSzH-hjC9wfU9vql6-Lr1Ql6gzgO9Lbnk4mXiksZGgCOM4F0h4992P-v8eZh2ze0X1DSV9FQJBhZf6WlFeS-hn5s6sOk1cB_Sz72uu38Y1lm3pa8n9TfpDlfCMNU7bkyQpdAupB04iP2RTI3yWN5ZsC-CW0ALgkQfcXiwlccVdHuAA7hSPnBMYnxBPl1xUWp9WzBDEiZ9f5v0TaWWwhBAlZgVdC-VznsFbZC7V8kZOMKI1lLhDwWI2rZq0g-VOcjwIRgOh55RAGrQskH8j4haJkvaifN4R9oMSKIz05Cs9vgk79-Wck8vFSTKP3WIeJuRPz1y8yzi87B1CIse4P_-zYNibdwhQkjyDDmIkztoc1pH09rp3Hnhn6z07n4hHya_ahYfiphKCv4RePqk8ktuwpE7DUBdBEDLNZD7XT0FdACC2mgonr0ajA-V4MZkSIwMv1r6ZxWgSiIdOOyIyNZklkHgQzhplmlH1-_1D_SZQDIXE5N-k0EvoQokLvo6GhFfQA-AZVMXhpvHDPb7cYH_riMlwabBRORCWc92zOyVtm1Ftb79vil2RCkWnV78grVfrykEpoMk3NIRScNkX2pPxC_HQJTgXTTvf0iQ5APN_rECqMELAKp8glRWnPSI5bGTchNGxCz55L6Dbzp0UhBJwNSCddQQmjR10VMm1ilWkiXLj6d4D7d_FOcXVdyMxALDIaqgOgIV4M1E82ziL37ldy-iFxeQ0xE8gp2Hj2_VayqW2K0Ups2LHv9oDe7q6gRD63OcjJB2rARjRgYi3Pi0ISh6QLUaLmaib-clRSX17b5mcAdIOAUEXnhseX0W386i4vV7hsO7yVEH6tcQwcShloVE80LwSGnXOhLalCWEkjqDnK_JXmcYhGh2nT_QqDrZ2nr2yooYyxST3qK9jqn0LzZnIaIFKF5RR-Ue2iJS7hmsAodtS2s1A3VOCJCOKBrBZIcjPyIDUNbUjhU-V8YboaEcNhuMiBRCiWwyu-Kw2iWMhP4BUc3ZMz43PnRCUfYzv2N8xIdSsECYOeOEhcRxvsLbGSR2J1jTMFD4_Cff3CRgyXuMIjAMYouCyfZKvilyoQucPDcYj-b_2tjHnX2QuSoHK-nAgie5LjOmk6S86HOAgXwIClO5HkaNvNEYO7rqsPxu823vcXzq5Wb0YinUlfLJvjqIKKihjaVyVkk4MJnVyEzv81TiHTBlzFW9SwstYdcGecXCgnKMQfM-Y2T5vDfZc0A9bkUjYr__OKNutGZGNfLo5gU8A=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The request has two material conflicts: 500 invitations cannot cover 650 guests if every guest must receive one, and \u201cindividually addressed\u201d conflicts with using exactly the same text with no variable printing. The delivery instruction also says your office will mail them, so it is unclear whether the supplier should print addresses at all.\",\"text\":\"Should the quoted quantity be 650 invitations, and do you want the supplier to print each recipient\u2019s address (which requires variable data), or should all invitations be identical and unaddressed for your office to address and mail?\"}", "call_id": "call_UOJ6McM9alRrOgSWrrRSliAm", "id": "fc_0795837696be5b5c006ab5a360b44c87d29034e02c4151750a", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The request has two material conflicts: 500 invitations cannot cover 650 guests if every guest must receive one, and \u201cindividually addressed\u201d conflicts with using exactly the same text with no variable printing. The delivery instruction also says your office will mail them, so it is unclear whether the supplier should print addresses at all.", "text": "Should the quoted quantity be 650 invitations, and do you want the supplier to print each recipient\u2019s address (which requires variable data), or should all invitations be identical and unaddressed for your office to address and mail?"}, "id": "call_UOJ6McM9alRrOgSWrrRSliAm", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -373,24 +373,14 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d133-118a-7ce3-a1cf-76986af715ce</t>
+    <t>01a0d586-650a-7112-8b67-eccdf97e95f7</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>[{"id": "rs_0a7e38912863ce39006ab487f500a487d29fc0a39c06c94d65", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIf4hgNhLoT9OZru5REcX-pIxfrRw0fVUb_GeNBBzJ4SDZEVdnV-xodhbRl9AcfhG-Zq9xqUPpULTGxdzD5SZ4-uwXQ_T45ymrvnmyyvE7XYPL-_M3Myvsu9hT6n55-hQ9lgi--r17R8qHoydqjMdykdykCTgf1G61uzceFo_dZIMYsuQ92rBHq9Apdnxei_Q5rHo_ZAgxnhFwCb206b5hobit9_WxdLoF38untW8-DXRBCFIBkT1hAvQ6tSE3qKXcrMd5pjHp_1jvpfuLx3KJ_gTPrGrwI6JB5xvg-aNzBx1oST3HrBiby9Q2wTYApmJKw2_V4M5Mhw51srAYB2KdRYXYBLMTnKFQWGMzIWPpQLXG37T5RbQ8LO8Tjh_kJRBfwvI4hPJ193O1tuveQa7RPGW2MHcquBPpGuXD5wLsdmsGkhtP3wqcirBTU5zsC5HyZXwQtnIuiaOB2lyaxpAXs7qHmt2L61tT5jEea3SQObJpkuamD4aOpyZVDh5hlkbDcY7pjVVLHETDgxiX-DeCMEQgYWc9kC0UgqMesouz6s7Mycg6apGGyRcUbNpFXw9O-1rk9_JSWmAuukqjwd1V0JYIXfKJ4OUCKYX38V18dBKLd3g_gsL_s3kc7sXD-gtxtVgfJbBAihN6s_zxgcR68j2v-DetUwAlg7vzBlhD1zDklxwBnjGFdexE2m5mAWG4lNyZG5JwmXWdFA0nLVCu7IKgyDJXu2TQ3UqJmwoNhAQjWqx3sRD9WkVkt8ovkDtjPwXbNGiqdBBquHdggWwxMM9mYzVs3y1OnDO5pDu8YX87FPGpY4A24-x7YQ06o5DxbEIr_U8r72MQRZEs1NC1wgpOe_IlsPu1XzgVIFILv8IjczT_U0ejkGwlcnN581IWeVjTO6D29VNx8DOx4Hd22tisW_HjvRd9AAXfQ_PRJMKvVjhf-MV2NpiqVGTgud83fO2H6v5n3K11fDuODcJYdU5p7n_A2RZvqKaqII58z_n9PFTaQSQKuiOmGFeUMpFMuxuFwCmNAVrSgpYNx74U_lCwIWeKCtM_VNdRA3q2hundjzeR6lIhRVticxdhQ27maWhl7U7UJaxLMyWyuXxLdy00UkQz6lnzKEVzpBq_vhNr8BSifouNdZJBm8fLzTB5FDCr650uLxNd-T_ftmJ2ZDi_l1wYecKEry2_9kCeJRv-odOGX2urqc9s5kfcrDHYRWu_TxNkfu7kQufBcHRvTZMasiN8_YJl77Z6QLoubxEbOAsrKgGD0hv0I0rPzsvvU67dtD20fhXwDPr4Gnxf0gm5ETegl07N8m1VW94pqCxRbVY1SjY3O78fkRKPkp6StzQgCPpWs4iARGFXU1VBOX03f5fM8UzYLAdUx4ldoPnJpttwiYPDJPiTfs76tC1zhBo8iCe4zqsj2_rIicRIhFaS1_OR4_ykn0OqIl6ty_mUTfJs-HfLvvR4YmM3mEnnp2TRmN9P_YbwFDjHBxaKi_OqbWjB42PxBCEulliNxcNMHw1MSLBSrskehLaShL60awDA_cJb2mZIAoOsQXiCXmR2CJFHWvbmvO2mYFz8WIp7OtnuB5obacvTIhpC-rZ_vJbqc9szTVXxV-l77XsBaEVB83G9sThqFCLJtZzhMIeQQOVjgKA7ozh58_K7kHrk2_-Rjn307ask1NUFZkxiAXLFxzBf2L-rLbBjjhfbdvfCm2cNtUlEqnGwteQ6H4HT8WV9PLxyVm8eR7Zv8ukJkTqVcUGTbWBvmgGtsinsOXs-T69Q0gNJ7HpOyXG7uKlCb9vjrntZF9tdjbKAjF8o9PnY5e-xdZf-X4LbPIFMx_ySHDeD7v1EiCl57XqmfFmCAJIWGOkQNrVkaHcgGrc_aZgajVFq3Vyd3rixB9-IvJ-DBfjeMu1JxEpHxbNcCTguOBJm4RK1sPub4JxEzMlRwpbGEFk72iNKidu5uc2ybr8XKRI6MH9e4r8zSXTg822zby_XH2v0njI0NPuE2ygiY6vodtFf_NDZ49azIUnWFeFF1ApK00O0oW_X7pw2Fc5x4c0klBXySLfBzH1cJsv156YnbKjPIO4J-PnWVTkbogCAEUJ2lKUzFA1Yq6e_KPgdjI95wlFZKTAJ8xw7hk44cT_PK8OFHKt5y1uXrqh9aFu1KWQcDdn0WNaJ9y_4H9wAtk9GN7HJJvYyZtQDkIdk23EcQy3fLQxDIEfGeg-j1pWObTEmqd9Y78noDWjtVpgILsnZa67_y3MvASfDCRDgTiEYELDxiOhkx_FHMS1QNHL8d3_EqIaKWcz6XV1UQkmdxiSprgXX15zTgmTGITQJ85IWKwHytLc4ZDiwYptUkgxt5OXAy5JTfteZL3_RSqo3mcBg_wMo-UOD1XmGOgczu1N91LJo9XjE00Lt0a5kf3yu547wdtrUnpm6NMue4WxFu4tKCVKzdqVYyg5o-Fe4OArT3ziETkx6gA11g5CWljsawsgdL2u8Ouem_1SE781Bo_bSb2qCSUb5e7-cnoxdhJfKFwhwzeBAsTCXoIkgyUdsxecikvMHiLPTyWfSuqEzkpozB_Xu6uMxUHD3jG9DBMgQ=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The quantity and addressing scope are now consistent: 500 household invitations, each with identical text, plus 500 envelopes addressed from the supplied spreadsheet. However, it is unclear whether the printer should assemble the pieces by inserting each invitation into its corresponding addressed envelope (and, if so, seal them), or deliver the invitations and addressed envelopes separately.\",\"text\":\"Should the printer insert each invitation into its matching addressed envelope and seal/assemble the 500 pieces, or should the invitations and addressed envelopes be delivered separately for your office to assemble?\"}", "call_id": "call_DQ45b1X9ULyLlOEg0TYixrZh", "id": "fc_0a7e38912863ce39006ab487f8560487d288cfa0b10851cfa1", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The quantity and addressing scope are now consistent: 500 household invitations, each with identical text, plus 500 envelopes addressed from the supplied spreadsheet. However, it is unclear whether the printer should assemble the pieces by inserting each invitation into its corresponding addressed envelope (and, if so, seal them), or deliver the invitations and addressed envelopes separately.", "text": "Should the printer insert each invitation into its matching addressed envelope and seal/assemble the 500 pieces, or should the invitations and addressed envelopes be delivered separately for your office to assemble?"}, "id": "call_DQ45b1X9ULyLlOEg0TYixrZh", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0d133-a99c-7e60-8aea-8333e658ca6a</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0a2c09f56a55c5db006ab4881c7a8487d28449fbe438a7f063", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIgeuA24LoKv2SpEH5gg6GH8x-b8bAffq_NCjlyJQxbVJkVy_TEV7v6Ov9NWCsHjCze6jgVrJ4nHeH92ximm_F5NJNFq9S8rdO_XqUYQqrvudrulGF6K7Fcnqk12ep8J5-IiiWDzzUydhWZQUE-o4x_UxZzCBpL_g2NcV90hb1fggPK7DAMIr8b0FYd85S42BXdrQuXoz1mKVmau_FKaP1eQYUFDlbhhD6vC1d3rp5IK8hTM8QrrESwfAjQrWm9viaWnlnj2fXuk2GcKm6zqxziDP5VXuD2cqOjYEcAENbm5E_L9D0YqIEP5MLpe6SzYalHkaAHugtMLp8I4hlwo4rYy7Su8Q_M7nuIAkTE3I-96G7WhoE3lCXztXOSMWEd3SPN2SUSp08g0TWVM4xZrZ9sceiVeolzfSqNHgS8E_WXE-2YjtIoKkmg0JyxMWNWTbHDas9XIejSeHO9ipL7FGcn1k257izjXPotPl4AVb_30EnUbTm72J11EBtPfaQ5QZSGBJGFvG9bPdGlM7btEUjg5ILDL7vRUD5w4CSU7ZPywcl4AYtZ9cyQctQDm4yoL6G53o9631eR-ALXfG9DRgUxn082FbKZ2sVEHJ6B6_oqVtMyVgX0HqkVAq4NOlFaIdMVQZQLpA3Jyq0RqVfrQcZuY9ANw0MVLSbuynIn39UPboCfQfVS2f9NnptcsLRfaEK42zwUt0CgT33dpecYbHQn0OWGIW2ncRpzcW307BURZUCuWsTinTpOFLj4ppX3kzQcpWd7zgGvibG4e_p8vf2RHyJ0Ef1gHtTTpkMPYKX5ZWdI0sPspnstzK3UyRFp-D_b1T3ltIF6pou_Z2Q3fd4wr3eGh7ReTET0OZaPbLBIcWIGcZfcK8d40FxFQVZZ12RL3EawfTntKxpFhi1sNqmsEvssLLmFGPku4Cp3KCBdaGtIAfoFG8SSwmlPm-VZAJ-doc0nXXD6BZBVKluehwgw1nyZkIU0So8dopy-xacVtjYwIm_Vk0HaLbkzG8Ygz13Ta7VTOvbIekfqkXZleb7I88hI5cHkr28qYuEY83qsDSqgLlMJ8EhAHy4FjFYCMqpOEHK2L6Z0M8m1x0Qm91trIi6cViAU21stQT9wOLr6GrSG79H3qRCQDS_1OwQLoyHC1PNeZJwdcPTvYu7sDQX2fWyjBAgdXO6H5xldO2wuGPxfnDyCZvwiNmLxz3obNqyu3X5pxzbeHlFfiz9YwukzhiwMY5pY5X4eu1KwIumpY5bQt_C0bTnY9vEnHVNVOHVMjK04YDdRS1U8Shuwwh3aMF1y96qwnGz95OBNQH6LzHgJOnfrD2Hc-6pPUEr0GD6h0JImkT8H_3sQ94udDf1MKkBDeDoVXy8ffnSHQGTx9UtLQnp_rTF0H7k9Oil-ClH2fUc4Mg4D58jH-RncClGukYE_xqnJpIDiPEl5CugAslg5Pzv_mPT6Hefse5PrVkGpUqmwcMunXBAlNATUK-yOLCYUJ6qP36e6VgKrIQDxk3ZxIHjP4e5BNCrD_Y-aN49eT7YzHyJX-A58q3IoitR9OqSwz213UcD28DjpBQmwUyM18y35PhcRpPiiKFjyB_zyh3ungUXFLeD04_jCL0vMy_fl1RA1Bf6aa-KuhujulcjKvxAgPMoQ97Ktw-Mzj_u7YD94yqN0bw4aq7s1uHFkz9-lc5Niz6puWvB2Q3fbw30lZQrMx_o9zKtj9bEOb5zKab1YMCM3MtoIM_CoEU8tnQO5x2NE_UMVDGeuFgBS02KsLUs_Vv7Jef3UWUEgK_4_GjMffuNokwM9SDXpPZ-Fc6pu2Fg0Fh3Xb_g3CbHLIZuFNOPb5giQdUPnHMm5Di3lUASuUBOAIxoPVeorGPmbQEWH8V0uWJIQB4_NBIzTUpJZ-KqclCUKA5jPeN_I9r6xp"}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"ask\",\"reason\":\"The quantity and addressing method are clear: 500 identical invitations, one per household, with 500 addressed envelopes for 650 guests. However, it is still unclear whether the printer should insert each invitation into its matching envelope (and possibly seal them) or deliver the invitations and addressed envelopes separately for your office to assemble before mailing.\",\"text\":\"Should the printer deliver 500 invitations and 500 addressed envelopes separately, or insert each invitation into its matching envelope (and seal them) before sending the batch to your office?\"}", "call_id": "call_5bIEcg65zxEWxporkThfN2EP", "id": "fc_0a2c09f56a55c5db006ab4881e329487d2a40a9c9d6e7d471d", "index": 1}]
-{"name": "QuoteDecision", "args": {"action": "ask", "reason": "The quantity and addressing method are clear: 500 identical invitations, one per household, with 500 addressed envelopes for 650 guests. However, it is still unclear whether the printer should insert each invitation into its matching envelope (and possibly seal them) or deliver the invitations and addressed envelopes separately for your office to assemble before mailing.", "text": "Should the printer deliver 500 invitations and 500 addressed envelopes separately, or insert each invitation into its matching envelope (and seal them) before sending the batch to your office?"}, "id": "call_5bIEcg65zxEWxporkThfN2EP", "type": "tool_call"}</t>
+    <t>[{"id": "rs_07e1467c2e1bc806006ab5a36e6c5487d2911b18dc8a9fd786", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaNvFGn2IyTOsbBW7qcWybEEXD4VSoii48ErZCtn_id50myuKZswi713sMYvmgJJ8dRW1msbHxRodvjII-fTRjac2mfJeBoFy6dwF3cwkhZtonwTRdG9gZF7MJG5lUaj58u1dY-MQoMEXHo7sY_XzPBF3s_OjjvJSHHYTDDfHnZ7EMFIOBArhV7frcl7srTHSUfzhOxDZDF3Ar2f76BoxOTggHiTKfGR_xHKzmHSNdBlC3e2pgAeXTG0f8-dZY_uh_opPoNLlIn9VwvXIQjuuCL5zk5gXOTygqrZMCOZ2xW_xNaPNBaGL2PYVVXym57KkhtK9ZlcBGftJhqmpdu_vD8mG7ORZF784P6Gqqm8AgAxxPl4ezpE9uuFm-gLnZZGQrZ822nDKbzkmDeUJf2GariLbvC0qiMEVNvTB32EwX7hB2asGTyIcDF8DYnWDr9wHPr4ggKo8RzMRwaSYUfWBWf_pQ_o67xDBGMuDHALdEDqJSXw8Bmn1Jo5dFFdLRECdmmUnbTc5uh0KM4FcLBntcUhj-9rCtxecy8vIGRqM52IdD0GKCJrtB_hSmgixe46pu42vSvJopnRvEBRIu0fXGyikWYuTEEsWgL9B1Kd2LkHh6mzsJ4fbFFikIM6zIB_8O8IC8Q0ckeQ3MleExNFIMPIWh_MW-6gO_kq5_986eJfdH-yg9iiBDLb29O3EBGRKqc_imnP2KRCeb1W2DTaMWOxlF7Z8vDFDScCVJ-xmc6GuWZi0DgbhqoeyC85nsOvN3Y0jL4O7Xlh-dDU3SAmmYUnbEfVXasx8Qcrht2QMV4u3hoHujRMwOv2jfBHPZ_Y7RynyABMVbO_kn3mioic3cfaIpto3pMr-T00E63WT7jXNdd_iOdP-CSTsAi_SnXxlCSATB-Hz2AqaHErqTSJJTkxxCm3bq9NfdU_Aoi8MnmBj-ZTIOL6FULxLwq8qmIsx4hUZQ7LIRzoIjxa4ZfrdrxlRbzQ17dT7qYRBV8w1cAdZjqJ2EPEyMxwV6fHmqKQypXOi-0-N6U8SiZ9RUNuwe1201L46npGujaeC1B0qDdBtf_tvviyYJGy-UR6RRNHhNrwnz1RBtQ12mlaY6eRFqMIWNd7guQ_71cjAYXMg3yJQOrJJu_r6RbNl4QnYUeZIvl5VEVQKOVix5YTh5kKtsL6t7QMnDWBxJPQ4UyG7x0pA9gBDPR-XBqUM9sSi1Dn7ntY5vziqnOnLvpyG8y2LjVXoKzzIer1ItiloXXwdeXSPZ6WgPBZVgdqxgJ_gGuHyuW6JF3UonHXfoQnvvU_6Gg9OVCe5aSNwNFi0B5O78qCHM3dnf2vIEhmU9wfDaOMqY5e7cY8oLFzBA8WW6da9pmJDN0sUJ4my4Tt5Ed_9JoEOs3bfNrWsEhCPP7yNtr8BUaoHE4ALtmynKb8Jrb9miXdYNf7LWQjNijvJhyE3otrSixWN2xBHZjH1fhOc-kJ-yLkhSWaRrJXWHSF2zbrVrk8UWB60WSPC6LCTiQ-bkDvaVpHkRBxhGhKEsk7V2IQxe3cE5WEj-G31tiT0ZGQDfl0o7CyvujdTQjOA45v6065--AP3V7Y3R2P2tjTuMgTWI1PpzLRfanH6ufJw8FdXNlb9OIQoYZiLbGBlHyYyJsMOzG-ed-UdjkzvzoHi0g8r3SMwOfPV_znV4tkc_BfzbsHZEkizj7oAU2O08_gg48lsrqu-bTVxBkW_Belp3de6UU9kwdJAjmON7dH5_Sn2e5SaRx54WQjkiZhsNlCqqcL7FsCUj403dJXTtDusIsOBlHBZGEn2Ld-LB6oMxe3xwJqn49qrEoWaQaQC5_NgLsYqhqVUrISRjCQ1nM1ksoy7nudkrL6Yvi5TmMHBq2qoI3jQwl5Zx2WxXmiQdmOoasaOuWzIbXH6QGI2jG5tqmFq3FqbLNL14zEBdZyHsjmF9m2aQ=="}, {"type": "function_call", "name": "QuoteDecision", "arguments": "{\"action\":\"complete\",\"reason\":\"The clarification resolves the apparent quantity and personalization conflict: the 650 guests are grouped into 500 households, with one invitation per household. The invitation text remains identical, while each of 500 envelopes is personalized with the household name and address from the supplied spreadsheet. Delivery is one batch to the office for self-mailing.\",\"text\":\"Please quote 500 identical invitations and 500 printed, individually addressed envelopes, using the customer-supplied spreadsheet of 500 household names and addresses. Deliver the complete batch to our office; we will mail it ourselves. No variable printing is needed on the invitations.\"}", "call_id": "call_D7m8nMhebMx9AazzLEsIXGs7", "id": "fc_07e1467c2e1bc806006ab5a36fa4e887d2b40038750e049eb7", "index": 1}]
+{"name": "QuoteDecision", "args": {"action": "complete", "reason": "The clarification resolves the apparent quantity and personalization conflict: the 650 guests are grouped into 500 households, with one invitation per household. The invitation text remains identical, while each of 500 envelopes is personalized with the household name and address from the supplied spreadsheet. Delivery is one batch to the office for self-mailing.", "text": "Please quote 500 identical invitations and 500 printed, individually addressed envelopes, using the customer-supplied spreadsheet of 500 household names and addresses. Deliver the complete batch to our office; we will mail it ourselves. No variable printing is needed on the invitations."}, "id": "call_D7m8nMhebMx9AazzLEsIXGs7", "type": "tool_call"}</t>
   </si>
   <si>
     <t>LangGraph</t>
@@ -411,7 +401,7 @@
     <t>Execute the begin workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d132-b476-7663-a711-a6b17af32faf</t>
+    <t>01a0d586-29ac-73e0-aa12-7e0d4b78443c</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -423,7 +413,7 @@
     <t>Execute the assess workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d132-b478-7dc2-ba3f-c8229bf4d00f</t>
+    <t>01a0d586-29ad-7f00-933f-4a1869c6f01a</t>
   </si>
   <si>
     <t xml:space="preserve">        quote_interpreter</t>
@@ -432,19 +422,19 @@
     <t>Interpret quote scope and request human clarification when needed.</t>
   </si>
   <si>
-    <t>01a0d132-b478-7dc2-ba3f-c83965587b76</t>
+    <t>01a0d586-29ae-7d31-8584-22502446603a</t>
   </si>
   <si>
     <t xml:space="preserve">            quote_interpreter</t>
   </si>
   <si>
-    <t>01a0d132-b479-7172-a853-94c430ea0c22</t>
+    <t>01a0d586-29ae-7d31-8584-22668b17cf65</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0d132-b479-7172-a853-94d1a50047c4</t>
+    <t>01a0d586-29b0-77b2-86c2-2adc71e0623c</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -462,7 +452,7 @@
     <t>Execute the route_after_assessment workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d132-c37a-7e32-983e-5632d71a7d69</t>
+    <t>01a0d586-36e4-7c81-ba1c-002eabcf0010</t>
   </si>
   <si>
     <t xml:space="preserve">    ask</t>
@@ -474,13 +464,13 @@
     <t>Execute the ask workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d132-c37b-7222-8913-854965114e1e</t>
-  </si>
-  <si>
-    <t>01a0d133-117e-7412-a0e6-e01193fa09a8</t>
-  </si>
-  <si>
-    <t>01a0d133-117f-7d83-aa06-63185f83ad93</t>
+    <t>01a0d586-36e6-7a91-ab82-0cddd71acbfa</t>
+  </si>
+  <si>
+    <t>01a0d586-64fc-76c0-9a93-52b55355d776</t>
+  </si>
+  <si>
+    <t>01a0d586-64fe-79e0-92c7-7d635e5b7943</t>
   </si>
   <si>
     <t xml:space="preserve">        route_after_answer</t>
@@ -489,61 +479,31 @@
     <t>Execute the route_after_answer workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d133-1180-7270-866d-0c9dd907bde1</t>
-  </si>
-  <si>
-    <t>01a0d133-1184-7871-b971-e47d33011813</t>
-  </si>
-  <si>
-    <t>01a0d133-1185-7b63-bb1f-e8eefc719b54</t>
-  </si>
-  <si>
-    <t>01a0d133-1186-7842-b2fa-bed9045fbb69</t>
-  </si>
-  <si>
-    <t>01a0d133-1189-7511-974a-d5358dde7c37</t>
-  </si>
-  <si>
-    <t>01a0d133-293b-7c40-b4c1-4ab184998a15</t>
-  </si>
-  <si>
-    <t>01a0d133-293d-7640-b1f5-6d6a5e4cf7fa</t>
-  </si>
-  <si>
-    <t>01a0d133-a990-7020-bcb1-e6bdf0ea3b0c</t>
-  </si>
-  <si>
-    <t>01a0d133-a993-7572-83c9-41bb34523e45</t>
-  </si>
-  <si>
-    <t>01a0d133-a994-7192-af2f-8c42f1fa2726</t>
-  </si>
-  <si>
-    <t>01a0d133-a997-7f12-a380-e6d1a5350a86</t>
-  </si>
-  <si>
-    <t>01a0d133-a998-7eb1-a02c-60bfd6776ae5</t>
-  </si>
-  <si>
-    <t>01a0d133-a99a-75a1-ae01-3125ed1cdf9f</t>
-  </si>
-  <si>
-    <t>01a0d133-a99b-7f83-a110-9f23643bd343</t>
-  </si>
-  <si>
-    <t>01a0d133-bb75-7d21-9e45-fe5f7dc4d9e9</t>
-  </si>
-  <si>
-    <t>01a0d133-bb78-7f83-be1f-0e66998fc57b</t>
-  </si>
-  <si>
-    <t>01a0d134-1e7b-72a0-a391-742e647aa97d</t>
-  </si>
-  <si>
-    <t>01a0d134-1e7e-7a73-b27e-6a89544ed930</t>
-  </si>
-  <si>
-    <t>01a0d134-1e7f-7ae1-a52d-3808669adb78</t>
+    <t>01a0d586-64ff-7b42-96a5-ca7b52101fae</t>
+  </si>
+  <si>
+    <t>01a0d586-6505-72d2-a28a-c2cf67362d5c</t>
+  </si>
+  <si>
+    <t>01a0d586-6506-75e0-b33a-9d881e387c1c</t>
+  </si>
+  <si>
+    <t>01a0d586-6507-74e2-9a36-c84f586a0943</t>
+  </si>
+  <si>
+    <t>01a0d586-6509-79c2-b34a-02dc7e39f31d</t>
+  </si>
+  <si>
+    <t>01a0d586-712c-7ba1-89f2-1205dfba65b2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    complete</t>
+  </si>
+  <si>
+    <t>Execute the complete workflow operation and pass its result to the next graph step.</t>
+  </si>
+  <si>
+    <t>01a0d586-712e-7351-92af-152a88fad5c0</t>
   </si>
 </sst>
 </file>
@@ -950,7 +910,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1010,20 +970,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
-        <v>0.0010603835</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
+        <v>0.000696930028</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
-        <v>0.00121</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
+        <v>0.0007922</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>106.0</v>
+        <v>70.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>121.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1034,20 +994,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E29,'Turns'!E41)=3,SUM('Turns'!E17,'Turns'!E29,'Turns'!E41),"Unknown")</f>
-        <v>0.0010603835</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E29)=2,SUM('Turns'!E17,'Turns'!E29),"Unknown")</f>
+        <v>0.000696930028</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F29,'Turns'!F41)=3,SUM('Turns'!F17,'Turns'!F29,'Turns'!F41),"Unknown")</f>
-        <v>0.00121</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F29)=2,SUM('Turns'!F17,'Turns'!F29),"Unknown")</f>
+        <v>0.0007922</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>106.0</v>
+        <v>70.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>121.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1085,7 +1045,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1172,7 +1132,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1186,23 +1146,23 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1216,23 +1176,23 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409" customHeight="1">
@@ -1283,19 +1243,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1312,7 +1272,7 @@
         <v>94</v>
       </c>
       <c r="D18" s="4">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>95</v>
@@ -1362,15 +1322,15 @@
         <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E20" s="2">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER('Reference data'!$B$3)),F20*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="F20" s="2">
         <f>IF(D20=0,0,IF(ISNUMBER('Reference data'!B17),D20*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="G20" s="5">
         <f>IF(ISNUMBER(E20),ROUND(E20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1414,7 +1374,7 @@
         <v>105</v>
       </c>
       <c r="D23" s="4">
-        <v>311</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
@@ -1428,23 +1388,23 @@
         <v>106</v>
       </c>
       <c r="D24" s="5">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="F24" s="2">
         <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!F17),D24*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="G24" s="5">
         <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="H24" s="5">
         <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
@@ -1458,23 +1418,23 @@
         <v>107</v>
       </c>
       <c r="D25" s="5">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E25" s="2">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="F25" s="2">
         <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!E17),D25*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="G25" s="5">
         <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H25" s="5">
         <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409" customHeight="1">
@@ -1525,268 +1485,26 @@
       </c>
       <c r="E29" s="2">
         <f>IF(COUNT('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25)=4,SUM('Turns'!E19,'Turns'!E20,'Turns'!E24,'Turns'!E25),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="F29" s="2">
         <f>IF(COUNT('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25)=4,SUM('Turns'!F19,'Turns'!F20,'Turns'!F24,'Turns'!F25),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="4">
-        <v>662</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F31" s="2">
-        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!C17),D31*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="5">
-        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="5">
-        <v>662</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!B17),D32*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="24" customHeight="1">
-      <c r="A33" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="24" customHeight="1">
-      <c r="A34" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="4">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="24" customHeight="1">
-      <c r="A36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" s="5">
-        <v>100</v>
-      </c>
-      <c r="E36" s="2">
-        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="F36" s="2">
-        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!F17),D36*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.00012</v>
-      </c>
-      <c r="G36" s="5">
-        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H36" s="5">
-        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="24" customHeight="1">
-      <c r="A37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="5">
-        <v>127</v>
-      </c>
-      <c r="E37" s="2">
-        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="F37" s="2">
-        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!E17),D37*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="G37" s="5">
-        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="H37" s="5">
-        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="409" customHeight="1">
-      <c r="A38" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="24" customHeight="1">
-      <c r="A39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="24" customHeight="1">
-      <c r="A40" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="2">
-        <f>IF(COUNT('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37)=4,SUM('Turns'!E31,'Turns'!E32,'Turns'!E36,'Turns'!E37),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="F41" s="2">
-        <f>IF(COUNT('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37)=4,SUM('Turns'!F31,'Turns'!F32,'Turns'!F36,'Turns'!F37),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="H41" s="5">
-        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE41">
+  <conditionalFormatting sqref="A2:AE29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1800,7 +1518,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1907,13 +1625,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -1922,7 +1640,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -1933,7 +1651,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1959,60 +1677,60 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>3847.202</v>
+        <v>3388.058</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -2021,30 +1739,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.405</v>
+        <v>0.476</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -2053,10 +1771,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -2067,7 +1785,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2093,60 +1811,60 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>3843.273</v>
+        <v>3383.573</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>47</v>
@@ -2155,13 +1873,13 @@
         <v>111</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2169,7 +1887,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2195,60 +1913,60 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>3841.727</v>
+        <v>3381.904</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -2257,13 +1975,13 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" t="s">
         <v>131</v>
       </c>
-      <c r="H6" t="s">
-        <v>134</v>
-      </c>
       <c r="I6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J6" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2271,7 +1989,7 @@
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2297,60 +2015,60 @@
       </c>
       <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V6" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W6" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X6" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3840.677</v>
+        <v>3380.67</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -2359,13 +2077,13 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" t="s">
         <v>131</v>
-      </c>
-      <c r="H7" t="s">
-        <v>136</v>
-      </c>
-      <c r="I7" t="s">
-        <v>134</v>
       </c>
       <c r="J7" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2373,7 +2091,7 @@
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2399,60 +2117,60 @@
       </c>
       <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3838.793</v>
+        <v>3378.523</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>95</v>
@@ -2464,13 +2182,13 @@
         <v>493</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
         <v>96</v>
       </c>
       <c r="I8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2478,7 +2196,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>8.640811e-05</v>
+        <v>8.6742364e-05</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2504,63 +2222,63 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>116.0</v>
+        <v>136.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>0.00012198792</v>
+        <v>0.000143573568</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001392</v>
+        <v>0.0001632</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>61.0</v>
+        <v>90.0</v>
       </c>
       <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.414882e-05</v>
+        <v>9.501192e-05</v>
       </c>
       <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.32e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00027254485</v>
+        <v>0.000325327852</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000311</v>
+        <v>0.0003698</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD8" s="1">
-        <v>3837.028</v>
+        <v>3376.031</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -2569,62 +2287,62 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.302</v>
+        <v>0.32</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.457</v>
+        <v>0.401</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -2633,22 +2351,22 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J11" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M11" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2673,60 +2391,60 @@
       </c>
       <c r="S11" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T11" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U11" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V11" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W11" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X11" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y11" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z11" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>6080.118</v>
+        <v>3125.131</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -2735,30 +2453,30 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" t="s">
         <v>145</v>
       </c>
-      <c r="H12" t="s">
-        <v>148</v>
-      </c>
       <c r="I12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AD12" s="1">
-        <v>3.092</v>
+        <v>5.405</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>47</v>
@@ -2767,30 +2485,30 @@
         <v>111</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AD13" s="1">
-        <v>1.142</v>
+        <v>0.527</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -2799,25 +2517,25 @@
         <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J14" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2842,60 +2560,60 @@
       </c>
       <c r="S14" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T14" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U14" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V14" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W14" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X14" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>6072.375</v>
+        <v>3112.328</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -2904,25 +2622,25 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -2947,60 +2665,60 @@
       </c>
       <c r="S15" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T15" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U15" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V15" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W15" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X15" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>6070.035</v>
+        <v>3109.665</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -3009,25 +2727,25 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J16" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K16" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L16" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3052,60 +2770,60 @@
       </c>
       <c r="S16" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T16" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U16" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V16" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W16" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X16" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y16" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z16" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>6067.659</v>
+        <v>3107.373</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B17" s="1">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -3114,25 +2832,25 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I17" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J17" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K17" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L17" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M17" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3157,60 +2875,60 @@
       </c>
       <c r="S17" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T17" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U17" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V17" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W17" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X17" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y17" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z17" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>6064.297</v>
+        <v>3103.544</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>95</v>
@@ -3219,28 +2937,28 @@
         <v>111</v>
       </c>
       <c r="F18" s="1">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H18" t="s">
         <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J18" s="2">
         <f>IF(COUNT('Turns'!D20)=1,SUM('Turns'!D20),"Unknown")</f>
-        <v>605.0</v>
+        <v>600.0</v>
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E20)=1,SUM('Turns'!E20),"Unknown")</f>
-        <v>0.00010603835</v>
+        <v>0.0001055688</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F20)=1,SUM('Turns'!F20),"Unknown")</f>
-        <v>0.000121</v>
+        <v>0.00012</v>
       </c>
       <c r="M18" s="2">
         <f>IF(COUNT('Turns'!D19)=1,SUM('Turns'!D19),"Unknown")</f>
@@ -3265,63 +2983,63 @@
       </c>
       <c r="S18" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>130.0</v>
+        <v>143.0</v>
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0001367106</v>
+        <v>0.000150963384</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.0001716</v>
       </c>
       <c r="V18" s="2">
         <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>181.0</v>
+        <v>109.0</v>
       </c>
       <c r="W18" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>0.00019034322</v>
+        <v>0.000115069992</v>
       </c>
       <c r="X18" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>0.0002172</v>
+        <v>0.0001308</v>
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00043309217</v>
+        <v>0.000371602176</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0004942</v>
+        <v>0.0004224</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>112</v>
       </c>
       <c r="AD18" s="1">
-        <v>6061.903</v>
+        <v>3101.371</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -3330,909 +3048,55 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.465</v>
+        <v>0.533</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H20" t="s">
-        <v>157</v>
-      </c>
-      <c r="I20" t="s">
-        <v>147</v>
-      </c>
       <c r="AD20" s="1">
-        <v>0.538</v>
+        <v>1.474</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" ht="54" customHeight="1">
-      <c r="A21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K21" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L21" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>0</v>
-      </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T21" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U21" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V21" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W21" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X21" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB21" s="5">
-        <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>4584.89</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" ht="54" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H22" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>2.44</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" ht="54" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I23" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="54" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K24" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L24" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M24" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P24" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T24" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U24" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V24" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W24" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X24" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y24" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z24" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA24" s="5">
-        <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB24" s="5">
-        <f>IF(ISNUMBER(Z24),ROUND(Z24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>4574.805</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" ht="54" customHeight="1">
-      <c r="A25" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K25" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L25" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M25" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T25" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U25" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V25" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W25" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X25" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y25" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z25" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA25" s="5">
-        <f>IF(ISNUMBER(Y25),ROUND(Y25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB25" s="5">
-        <f>IF(ISNUMBER(Z25),ROUND(Z25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AD25" s="1">
-        <v>4571.756</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" ht="54" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K26" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L26" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M26" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T26" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U26" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V26" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W26" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X26" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y26" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z26" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA26" s="5">
-        <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB26" s="5">
-        <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>4569.265</v>
-      </c>
-      <c r="AE26" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" ht="54" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="1">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H27" t="s">
-        <v>164</v>
-      </c>
-      <c r="I27" t="s">
-        <v>163</v>
-      </c>
-      <c r="J27" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K27" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L27" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M27" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T27" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U27" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V27" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W27" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X27" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y27" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z27" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA27" s="5">
-        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB27" s="5">
-        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>4566.051</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="54" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="1">
-        <v>662</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H28" t="s">
-        <v>117</v>
-      </c>
-      <c r="I28" t="s">
-        <v>164</v>
-      </c>
-      <c r="J28" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>662.0</v>
-      </c>
-      <c r="K28" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00011602874</v>
-      </c>
-      <c r="L28" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001324</v>
-      </c>
-      <c r="M28" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>127.0</v>
-      </c>
-      <c r="T28" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>0.00013355574</v>
-      </c>
-      <c r="U28" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>0.0001524</v>
-      </c>
-      <c r="V28" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W28" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000105162</v>
-      </c>
-      <c r="X28" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00012</v>
-      </c>
-      <c r="Y28" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>0.00035474648</v>
-      </c>
-      <c r="Z28" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>0.0004048</v>
-      </c>
-      <c r="AA28" s="5">
-        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AB28" s="5">
-        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>40.0</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>4563.701</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" ht="54" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>0.597</v>
-      </c>
-      <c r="AE29" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" ht="54" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H30" t="s">
-        <v>166</v>
-      </c>
-      <c r="I30" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>0.758</v>
-      </c>
-      <c r="AE30" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" ht="54" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>5.252</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" ht="54" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H32" t="s">
-        <v>168</v>
-      </c>
-      <c r="I32" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>2.306</v>
-      </c>
-      <c r="AE32" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" ht="54" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H33" t="s">
-        <v>169</v>
-      </c>
-      <c r="I33" t="s">
-        <v>168</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>0.487</v>
-      </c>
-      <c r="AE33" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE33">
+  <conditionalFormatting sqref="A2:AE20">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -4283,7 +3147,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>
